--- a/R8_県学調_答案番号整理ファイル.xlsx
+++ b/R8_県学調_答案番号整理ファイル.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{0CE79108-E243-40AA-A2FF-D4C43F8F3AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{168A5892-A067-45AE-82B0-0AE64295359B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2033EE3A-E66F-4EEA-A470-5CC6922D40C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27240" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="設定" sheetId="4" r:id="rId1"/>
@@ -5215,10 +5215,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A632EDD7-1943-4D3F-9110-F3182099B002}" name="テーブル3" displayName="テーブル3" ref="A6:I326" totalsRowShown="0">
   <autoFilter ref="A6:I326" xr:uid="{A632EDD7-1943-4D3F-9110-F3182099B002}">
@@ -5540,7 +5536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7287635F-B9AD-486B-B551-FBE980581C0B}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
@@ -5588,12 +5584,12 @@
         <v>盛岡</v>
       </c>
       <c r="M2" s="95" t="str" cm="1">
-        <f t="array" aca="1" ref="M2:M5" ca="1">IF(A5="","教育事務所未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"[教育委員会名]"),INDIRECT(C2&amp;"[事務所名]")=A5)))</f>
-        <v>花巻市</v>
+        <f t="array" aca="1" ref="M2:M9" ca="1">IF(A5="","教育事務所未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"[教育委員会名]"),INDIRECT(C2&amp;"[事務所名]")=A5)))</f>
+        <v>盛岡市</v>
       </c>
       <c r="N2" s="95" t="str" cm="1">
-        <f t="array" aca="1" ref="N2:N20" ca="1">IF(A8="","市町村未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[教育委員会名]")=A8)))</f>
-        <v>花巻市立花巻小学校</v>
+        <f t="array" aca="1" ref="N2:N43" ca="1">IF(A8="","市町村未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[教育委員会名]")=A8)))</f>
+        <v>盛岡市立仁王小学校</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -5607,11 +5603,11 @@
       </c>
       <c r="M3" s="95" t="str">
         <f ca="1"/>
-        <v>遠野市</v>
+        <v>岩手町</v>
       </c>
       <c r="N3" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立若葉小学校</v>
+        <v>盛岡市立城南小学校</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -5627,16 +5623,16 @@
       </c>
       <c r="M4" s="95" t="str">
         <f ca="1"/>
-        <v>北上市</v>
+        <v>雫石町</v>
       </c>
       <c r="N4" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立桜台小学校</v>
+        <v>盛岡市立桜城小学校</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="69" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="J5" s="109" t="s">
         <v>918</v>
@@ -5647,11 +5643,11 @@
       </c>
       <c r="M5" s="95" t="str">
         <f ca="1"/>
-        <v>西和賀町</v>
+        <v>葛巻町</v>
       </c>
       <c r="N5" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立南城小学校</v>
+        <v>盛岡市立厨川小学校</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -5662,9 +5658,13 @@
         <f ca="1"/>
         <v>宮古</v>
       </c>
+      <c r="M6" s="95" t="str">
+        <f ca="1"/>
+        <v>滝沢市</v>
+      </c>
       <c r="N6" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立湯口小学校</v>
+        <v>盛岡市立仙北小学校</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
@@ -5678,22 +5678,30 @@
         <f ca="1"/>
         <v>県北</v>
       </c>
+      <c r="M7" s="95" t="str">
+        <f ca="1"/>
+        <v>紫波町</v>
+      </c>
       <c r="N7" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立湯本小学校</v>
+        <v>盛岡市立杜陵小学校</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="69" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="L8" s="95" t="str">
         <f ca="1"/>
         <v>国独</v>
       </c>
+      <c r="M8" s="95" t="str">
+        <f ca="1"/>
+        <v>矢巾町</v>
+      </c>
       <c r="N8" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立矢沢小学校</v>
+        <v>盛岡市立山岸小学校</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
@@ -5701,9 +5709,13 @@
         <f ca="1"/>
         <v>県立</v>
       </c>
+      <c r="M9" s="95" t="str">
+        <f ca="1"/>
+        <v>八幡平市</v>
+      </c>
       <c r="N9" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立宮野目小学校</v>
+        <v>盛岡市立大慈寺小学校</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
@@ -5716,22 +5728,22 @@
       </c>
       <c r="N10" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立太田小学校</v>
+        <v>盛岡市立米内小学校</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="69" t="s">
-        <v>412</v>
+        <v>7</v>
       </c>
       <c r="N11" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立笹間第一小学校</v>
+        <v>盛岡市立土淵小学校</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N12" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立大迫小学校</v>
+        <v>盛岡市立中野小学校</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
@@ -5740,53 +5752,191 @@
       </c>
       <c r="N13" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立石鳥谷小学校</v>
+        <v>盛岡市立本宮小学校</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="96" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">IFERROR(IF(A11="","学校未選択",_xlfn.XLOOKUP(A11,INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[コード番号]"))),"選択条件が変わっています。上から順に選び直してください。")</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="N14" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立新堀小学校</v>
+        <v>盛岡市立青山小学校</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N15" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立八幡小学校</v>
+        <v>盛岡市立北厨川小学校</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N16" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立八重畑小学校</v>
+        <v>盛岡市立河北小学校</v>
       </c>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.4">
       <c r="N17" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市立東和小学校</v>
+        <v>盛岡市立上田小学校</v>
       </c>
     </row>
     <row r="18" spans="14:14" x14ac:dyDescent="0.4">
       <c r="N18" s="95" t="str">
         <f ca="1"/>
-        <v>花巻市教育委員会</v>
+        <v>盛岡市立山王小学校</v>
       </c>
     </row>
     <row r="19" spans="14:14" x14ac:dyDescent="0.4">
       <c r="N19" s="95" t="str">
         <f ca="1"/>
-        <v>中部教育事務所</v>
+        <v>盛岡市立緑が丘小学校</v>
       </c>
     </row>
     <row r="20" spans="14:14" x14ac:dyDescent="0.4">
       <c r="N20" s="95" t="str">
         <f ca="1"/>
-        <v>イーハトーブ小学校</v>
+        <v>盛岡市立太田小学校</v>
+      </c>
+    </row>
+    <row r="21" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N21" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立太田東小学校</v>
+      </c>
+    </row>
+    <row r="22" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N22" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立城北小学校</v>
+      </c>
+    </row>
+    <row r="23" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N23" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立大新小学校</v>
+      </c>
+    </row>
+    <row r="24" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N24" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立松園小学校</v>
+      </c>
+    </row>
+    <row r="25" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N25" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立月が丘小学校</v>
+      </c>
+    </row>
+    <row r="26" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N26" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立高松小学校</v>
+      </c>
+    </row>
+    <row r="27" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N27" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立東松園小学校</v>
+      </c>
+    </row>
+    <row r="28" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N28" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立見前小学校</v>
+      </c>
+    </row>
+    <row r="29" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N29" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立飯岡小学校</v>
+      </c>
+    </row>
+    <row r="30" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N30" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立羽場小学校</v>
+      </c>
+    </row>
+    <row r="31" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N31" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立永井小学校</v>
+      </c>
+    </row>
+    <row r="32" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N32" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立手代森小学校</v>
+      </c>
+    </row>
+    <row r="33" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N33" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立津志田小学校</v>
+      </c>
+    </row>
+    <row r="34" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N34" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立向中野小学校</v>
+      </c>
+    </row>
+    <row r="35" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N35" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立見前南小学校</v>
+      </c>
+    </row>
+    <row r="36" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N36" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立都南東小学校</v>
+      </c>
+    </row>
+    <row r="37" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N37" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立北松園小学校</v>
+      </c>
+    </row>
+    <row r="38" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N38" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立玉山小学校</v>
+      </c>
+    </row>
+    <row r="39" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N39" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立渋民小学校</v>
+      </c>
+    </row>
+    <row r="40" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N40" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立巻堀小学校</v>
+      </c>
+    </row>
+    <row r="41" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N41" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市立好摩小学校</v>
+      </c>
+    </row>
+    <row r="42" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N42" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡市教育委員会</v>
+      </c>
+    </row>
+    <row r="43" spans="14:14" x14ac:dyDescent="0.4">
+      <c r="N43" s="95" t="str">
+        <f ca="1"/>
+        <v>盛岡教育事務所</v>
       </c>
     </row>
   </sheetData>
@@ -5932,7 +6082,7 @@
       </c>
       <c r="B7">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C7" s="98" t="s">
         <v>582</v>
@@ -5942,7 +6092,7 @@
       </c>
       <c r="E7" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999001A</v>
+        <v>110101001A</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -5963,7 +6113,7 @@
       </c>
       <c r="B8">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C8" s="98" t="s">
         <v>583</v>
@@ -5973,7 +6123,7 @@
       </c>
       <c r="E8" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999002H</v>
+        <v>110101002H</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5994,7 +6144,7 @@
       </c>
       <c r="B9">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C9" s="98" t="s">
         <v>584</v>
@@ -6004,7 +6154,7 @@
       </c>
       <c r="E9" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999003K</v>
+        <v>110101003K</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -6026,7 +6176,7 @@
       </c>
       <c r="B10">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C10" s="98" t="s">
         <v>585</v>
@@ -6036,7 +6186,7 @@
       </c>
       <c r="E10" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999004M</v>
+        <v>110101004M</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -6057,7 +6207,7 @@
       </c>
       <c r="B11">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C11" s="98" t="s">
         <v>586</v>
@@ -6067,7 +6217,7 @@
       </c>
       <c r="E11" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999005N</v>
+        <v>110101005N</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -6088,7 +6238,7 @@
       </c>
       <c r="B12">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C12" s="98" t="s">
         <v>587</v>
@@ -6098,7 +6248,7 @@
       </c>
       <c r="E12" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999006R</v>
+        <v>110101006R</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -6119,7 +6269,7 @@
       </c>
       <c r="B13">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C13" s="98" t="s">
         <v>588</v>
@@ -6129,7 +6279,7 @@
       </c>
       <c r="E13" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999007V</v>
+        <v>110101007V</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -6150,7 +6300,7 @@
       </c>
       <c r="B14">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C14" s="98" t="s">
         <v>589</v>
@@ -6160,7 +6310,7 @@
       </c>
       <c r="E14" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999008X</v>
+        <v>110101008X</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -6181,7 +6331,7 @@
       </c>
       <c r="B15">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C15" s="98" t="s">
         <v>591</v>
@@ -6191,7 +6341,7 @@
       </c>
       <c r="E15" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999009A</v>
+        <v>110101009A</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -6212,7 +6362,7 @@
       </c>
       <c r="B16">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C16" s="98" t="s">
         <v>592</v>
@@ -6222,7 +6372,7 @@
       </c>
       <c r="E16" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999010H</v>
+        <v>110101010H</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -6243,7 +6393,7 @@
       </c>
       <c r="B17">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C17" s="98" t="s">
         <v>593</v>
@@ -6253,7 +6403,7 @@
       </c>
       <c r="E17" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999011K</v>
+        <v>110101011K</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -6274,7 +6424,7 @@
       </c>
       <c r="B18">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C18" s="98" t="s">
         <v>594</v>
@@ -6284,7 +6434,7 @@
       </c>
       <c r="E18" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999012M</v>
+        <v>110101012M</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -6305,7 +6455,7 @@
       </c>
       <c r="B19">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C19" s="98" t="s">
         <v>595</v>
@@ -6315,7 +6465,7 @@
       </c>
       <c r="E19" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999013N</v>
+        <v>110101013N</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -6336,7 +6486,7 @@
       </c>
       <c r="B20">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C20" s="98" t="s">
         <v>596</v>
@@ -6346,7 +6496,7 @@
       </c>
       <c r="E20" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999014R</v>
+        <v>110101014R</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -6367,7 +6517,7 @@
       </c>
       <c r="B21">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C21" s="98" t="s">
         <v>597</v>
@@ -6377,7 +6527,7 @@
       </c>
       <c r="E21" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999015V</v>
+        <v>110101015V</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -6398,7 +6548,7 @@
       </c>
       <c r="B22">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C22" s="98" t="s">
         <v>598</v>
@@ -6408,7 +6558,7 @@
       </c>
       <c r="E22" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999016X</v>
+        <v>110101016X</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -6429,7 +6579,7 @@
       </c>
       <c r="B23">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C23" s="98" t="s">
         <v>599</v>
@@ -6439,7 +6589,7 @@
       </c>
       <c r="E23" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999017A</v>
+        <v>110101017A</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -6460,7 +6610,7 @@
       </c>
       <c r="B24">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C24" s="98" t="s">
         <v>600</v>
@@ -6470,7 +6620,7 @@
       </c>
       <c r="E24" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999018H</v>
+        <v>110101018H</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -6491,7 +6641,7 @@
       </c>
       <c r="B25">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C25" s="98" t="s">
         <v>601</v>
@@ -6501,7 +6651,7 @@
       </c>
       <c r="E25" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999019K</v>
+        <v>110101019K</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -6522,7 +6672,7 @@
       </c>
       <c r="B26">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C26" s="98" t="s">
         <v>602</v>
@@ -6532,7 +6682,7 @@
       </c>
       <c r="E26" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999020M</v>
+        <v>110101020M</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -6553,7 +6703,7 @@
       </c>
       <c r="B27">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C27" s="98" t="s">
         <v>603</v>
@@ -6563,7 +6713,7 @@
       </c>
       <c r="E27" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999021N</v>
+        <v>110101021N</v>
       </c>
       <c r="I27" s="106"/>
     </row>
@@ -6573,7 +6723,7 @@
       </c>
       <c r="B28">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C28" s="98" t="s">
         <v>604</v>
@@ -6583,7 +6733,7 @@
       </c>
       <c r="E28" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999022R</v>
+        <v>110101022R</v>
       </c>
       <c r="I28" s="106"/>
     </row>
@@ -6593,7 +6743,7 @@
       </c>
       <c r="B29">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C29" s="98" t="s">
         <v>605</v>
@@ -6603,7 +6753,7 @@
       </c>
       <c r="E29" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999023V</v>
+        <v>110101023V</v>
       </c>
       <c r="I29" s="106"/>
     </row>
@@ -6613,7 +6763,7 @@
       </c>
       <c r="B30">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C30" s="98" t="s">
         <v>606</v>
@@ -6623,7 +6773,7 @@
       </c>
       <c r="E30" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999024X</v>
+        <v>110101024X</v>
       </c>
       <c r="I30" s="106"/>
     </row>
@@ -6633,7 +6783,7 @@
       </c>
       <c r="B31">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C31" s="98" t="s">
         <v>607</v>
@@ -6643,7 +6793,7 @@
       </c>
       <c r="E31" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999025A</v>
+        <v>110101025A</v>
       </c>
       <c r="I31" s="106"/>
     </row>
@@ -6653,7 +6803,7 @@
       </c>
       <c r="B32">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C32" s="98" t="s">
         <v>608</v>
@@ -6663,7 +6813,7 @@
       </c>
       <c r="E32" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999026H</v>
+        <v>110101026H</v>
       </c>
       <c r="I32" s="106"/>
     </row>
@@ -6673,7 +6823,7 @@
       </c>
       <c r="B33">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C33" s="98" t="s">
         <v>609</v>
@@ -6683,7 +6833,7 @@
       </c>
       <c r="E33" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999027K</v>
+        <v>110101027K</v>
       </c>
       <c r="I33" s="106"/>
     </row>
@@ -6693,7 +6843,7 @@
       </c>
       <c r="B34">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C34" s="98" t="s">
         <v>610</v>
@@ -6703,7 +6853,7 @@
       </c>
       <c r="E34" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999028M</v>
+        <v>110101028M</v>
       </c>
       <c r="I34" s="106"/>
     </row>
@@ -6713,7 +6863,7 @@
       </c>
       <c r="B35">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C35" s="98" t="s">
         <v>611</v>
@@ -6723,7 +6873,7 @@
       </c>
       <c r="E35" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999029N</v>
+        <v>110101029N</v>
       </c>
       <c r="I35" s="106"/>
     </row>
@@ -6733,7 +6883,7 @@
       </c>
       <c r="B36">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C36" s="98" t="s">
         <v>612</v>
@@ -6743,7 +6893,7 @@
       </c>
       <c r="E36" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999030R</v>
+        <v>110101030R</v>
       </c>
       <c r="I36" s="106"/>
     </row>
@@ -6753,7 +6903,7 @@
       </c>
       <c r="B37">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C37" s="98" t="s">
         <v>613</v>
@@ -6763,7 +6913,7 @@
       </c>
       <c r="E37" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999031V</v>
+        <v>110101031V</v>
       </c>
       <c r="I37" s="106"/>
     </row>
@@ -6773,7 +6923,7 @@
       </c>
       <c r="B38">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C38" s="98" t="s">
         <v>614</v>
@@ -6783,7 +6933,7 @@
       </c>
       <c r="E38" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999032X</v>
+        <v>110101032X</v>
       </c>
       <c r="I38" s="106"/>
     </row>
@@ -6793,7 +6943,7 @@
       </c>
       <c r="B39">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C39" s="98" t="s">
         <v>615</v>
@@ -6803,7 +6953,7 @@
       </c>
       <c r="E39" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999033A</v>
+        <v>110101033A</v>
       </c>
       <c r="I39" s="106"/>
     </row>
@@ -6813,7 +6963,7 @@
       </c>
       <c r="B40">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C40" s="98" t="s">
         <v>616</v>
@@ -6823,7 +6973,7 @@
       </c>
       <c r="E40" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999034H</v>
+        <v>110101034H</v>
       </c>
       <c r="I40" s="106"/>
     </row>
@@ -6833,7 +6983,7 @@
       </c>
       <c r="B41">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C41" s="98" t="s">
         <v>617</v>
@@ -6843,7 +6993,7 @@
       </c>
       <c r="E41" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999035K</v>
+        <v>110101035K</v>
       </c>
       <c r="I41" s="106"/>
     </row>
@@ -6853,7 +7003,7 @@
       </c>
       <c r="B42">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C42" s="98" t="s">
         <v>618</v>
@@ -6863,7 +7013,7 @@
       </c>
       <c r="E42" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999036M</v>
+        <v>110101036M</v>
       </c>
       <c r="I42" s="106"/>
     </row>
@@ -6873,7 +7023,7 @@
       </c>
       <c r="B43">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C43" s="98" t="s">
         <v>619</v>
@@ -6883,7 +7033,7 @@
       </c>
       <c r="E43" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999037N</v>
+        <v>110101037N</v>
       </c>
       <c r="I43" s="106"/>
     </row>
@@ -6893,7 +7043,7 @@
       </c>
       <c r="B44">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C44" s="98" t="s">
         <v>620</v>
@@ -6903,7 +7053,7 @@
       </c>
       <c r="E44" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999038R</v>
+        <v>110101038R</v>
       </c>
       <c r="I44" s="106"/>
     </row>
@@ -6913,7 +7063,7 @@
       </c>
       <c r="B45">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C45" s="98" t="s">
         <v>621</v>
@@ -6923,7 +7073,7 @@
       </c>
       <c r="E45" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999039V</v>
+        <v>110101039V</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -6933,7 +7083,7 @@
       </c>
       <c r="B46">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C46" s="98" t="s">
         <v>622</v>
@@ -6943,7 +7093,7 @@
       </c>
       <c r="E46" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999040X</v>
+        <v>110101040X</v>
       </c>
       <c r="I46" s="106"/>
     </row>
@@ -6953,7 +7103,7 @@
       </c>
       <c r="B47">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C47" s="98" t="s">
         <v>623</v>
@@ -6963,7 +7113,7 @@
       </c>
       <c r="E47" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999041A</v>
+        <v>110101041A</v>
       </c>
       <c r="I47" s="106"/>
     </row>
@@ -6973,7 +7123,7 @@
       </c>
       <c r="B48">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C48" s="98" t="s">
         <v>624</v>
@@ -6983,7 +7133,7 @@
       </c>
       <c r="E48" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999042H</v>
+        <v>110101042H</v>
       </c>
       <c r="I48" s="106"/>
     </row>
@@ -6993,7 +7143,7 @@
       </c>
       <c r="B49">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C49" s="98" t="s">
         <v>625</v>
@@ -7003,7 +7153,7 @@
       </c>
       <c r="E49" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999043K</v>
+        <v>110101043K</v>
       </c>
       <c r="I49" s="106"/>
     </row>
@@ -7013,7 +7163,7 @@
       </c>
       <c r="B50">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C50" s="98" t="s">
         <v>626</v>
@@ -7023,7 +7173,7 @@
       </c>
       <c r="E50" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999044M</v>
+        <v>110101044M</v>
       </c>
       <c r="I50" s="106"/>
     </row>
@@ -7033,7 +7183,7 @@
       </c>
       <c r="B51">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C51" s="98" t="s">
         <v>627</v>
@@ -7043,7 +7193,7 @@
       </c>
       <c r="E51" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999045N</v>
+        <v>110101045N</v>
       </c>
       <c r="I51" s="106"/>
     </row>
@@ -7053,7 +7203,7 @@
       </c>
       <c r="B52">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C52" s="98" t="s">
         <v>628</v>
@@ -7063,7 +7213,7 @@
       </c>
       <c r="E52" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999046R</v>
+        <v>110101046R</v>
       </c>
       <c r="I52" s="106"/>
     </row>
@@ -7073,7 +7223,7 @@
       </c>
       <c r="B53">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C53" s="98" t="s">
         <v>629</v>
@@ -7083,7 +7233,7 @@
       </c>
       <c r="E53" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999047V</v>
+        <v>110101047V</v>
       </c>
       <c r="I53" s="106"/>
     </row>
@@ -7093,7 +7243,7 @@
       </c>
       <c r="B54">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C54" s="98" t="s">
         <v>630</v>
@@ -7103,7 +7253,7 @@
       </c>
       <c r="E54" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999048X</v>
+        <v>110101048X</v>
       </c>
       <c r="I54" s="106"/>
     </row>
@@ -7113,7 +7263,7 @@
       </c>
       <c r="B55">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C55" s="98" t="s">
         <v>631</v>
@@ -7123,7 +7273,7 @@
       </c>
       <c r="E55" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999049A</v>
+        <v>110101049A</v>
       </c>
       <c r="I55" s="106"/>
     </row>
@@ -7133,7 +7283,7 @@
       </c>
       <c r="B56">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C56" s="98" t="s">
         <v>632</v>
@@ -7143,7 +7293,7 @@
       </c>
       <c r="E56" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999050H</v>
+        <v>110101050H</v>
       </c>
       <c r="I56" s="106"/>
     </row>
@@ -7153,7 +7303,7 @@
       </c>
       <c r="B57">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C57" s="98" t="s">
         <v>633</v>
@@ -7163,7 +7313,7 @@
       </c>
       <c r="E57" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999051K</v>
+        <v>110101051K</v>
       </c>
       <c r="I57" s="106"/>
     </row>
@@ -7173,7 +7323,7 @@
       </c>
       <c r="B58">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C58" s="98" t="s">
         <v>634</v>
@@ -7183,7 +7333,7 @@
       </c>
       <c r="E58" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999052M</v>
+        <v>110101052M</v>
       </c>
       <c r="I58" s="106"/>
     </row>
@@ -7193,7 +7343,7 @@
       </c>
       <c r="B59">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C59" s="98" t="s">
         <v>635</v>
@@ -7203,7 +7353,7 @@
       </c>
       <c r="E59" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999053N</v>
+        <v>110101053N</v>
       </c>
       <c r="I59" s="106"/>
     </row>
@@ -7213,7 +7363,7 @@
       </c>
       <c r="B60">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C60" s="98" t="s">
         <v>636</v>
@@ -7223,7 +7373,7 @@
       </c>
       <c r="E60" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999054R</v>
+        <v>110101054R</v>
       </c>
       <c r="I60" s="106"/>
     </row>
@@ -7233,7 +7383,7 @@
       </c>
       <c r="B61">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C61" s="98" t="s">
         <v>637</v>
@@ -7243,7 +7393,7 @@
       </c>
       <c r="E61" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999055V</v>
+        <v>110101055V</v>
       </c>
       <c r="I61" s="106"/>
     </row>
@@ -7253,7 +7403,7 @@
       </c>
       <c r="B62">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C62" s="98" t="s">
         <v>638</v>
@@ -7263,7 +7413,7 @@
       </c>
       <c r="E62" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999056X</v>
+        <v>110101056X</v>
       </c>
       <c r="I62" s="106"/>
     </row>
@@ -7273,7 +7423,7 @@
       </c>
       <c r="B63">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C63" s="98" t="s">
         <v>639</v>
@@ -7283,7 +7433,7 @@
       </c>
       <c r="E63" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999057A</v>
+        <v>110101057A</v>
       </c>
       <c r="I63" s="106"/>
     </row>
@@ -7293,7 +7443,7 @@
       </c>
       <c r="B64">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C64" s="98" t="s">
         <v>640</v>
@@ -7303,7 +7453,7 @@
       </c>
       <c r="E64" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999058H</v>
+        <v>110101058H</v>
       </c>
       <c r="I64" s="106"/>
     </row>
@@ -7313,7 +7463,7 @@
       </c>
       <c r="B65">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C65" s="98" t="s">
         <v>641</v>
@@ -7323,7 +7473,7 @@
       </c>
       <c r="E65" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999059K</v>
+        <v>110101059K</v>
       </c>
       <c r="I65" s="106"/>
     </row>
@@ -7333,7 +7483,7 @@
       </c>
       <c r="B66">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C66" s="98" t="s">
         <v>642</v>
@@ -7343,7 +7493,7 @@
       </c>
       <c r="E66" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999060M</v>
+        <v>110101060M</v>
       </c>
       <c r="I66" s="106"/>
     </row>
@@ -7353,7 +7503,7 @@
       </c>
       <c r="B67">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C67" s="98" t="s">
         <v>643</v>
@@ -7363,7 +7513,7 @@
       </c>
       <c r="E67" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999061N</v>
+        <v>110101061N</v>
       </c>
       <c r="I67" s="106"/>
     </row>
@@ -7373,7 +7523,7 @@
       </c>
       <c r="B68">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C68" s="98" t="s">
         <v>644</v>
@@ -7383,7 +7533,7 @@
       </c>
       <c r="E68" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999062R</v>
+        <v>110101062R</v>
       </c>
       <c r="I68" s="106"/>
     </row>
@@ -7393,7 +7543,7 @@
       </c>
       <c r="B69">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C69" s="98" t="s">
         <v>645</v>
@@ -7403,7 +7553,7 @@
       </c>
       <c r="E69" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999063V</v>
+        <v>110101063V</v>
       </c>
       <c r="I69" s="106"/>
     </row>
@@ -7413,7 +7563,7 @@
       </c>
       <c r="B70">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C70" s="98" t="s">
         <v>646</v>
@@ -7423,7 +7573,7 @@
       </c>
       <c r="E70" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999064X</v>
+        <v>110101064X</v>
       </c>
       <c r="I70" s="106"/>
     </row>
@@ -7433,7 +7583,7 @@
       </c>
       <c r="B71">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C71" s="98" t="s">
         <v>647</v>
@@ -7443,7 +7593,7 @@
       </c>
       <c r="E71" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999065A</v>
+        <v>110101065A</v>
       </c>
       <c r="I71" s="106"/>
     </row>
@@ -7453,7 +7603,7 @@
       </c>
       <c r="B72">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C72" s="98" t="s">
         <v>648</v>
@@ -7463,7 +7613,7 @@
       </c>
       <c r="E72" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999066H</v>
+        <v>110101066H</v>
       </c>
       <c r="I72" s="106"/>
     </row>
@@ -7473,7 +7623,7 @@
       </c>
       <c r="B73">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C73" s="98" t="s">
         <v>649</v>
@@ -7483,7 +7633,7 @@
       </c>
       <c r="E73" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999067K</v>
+        <v>110101067K</v>
       </c>
       <c r="I73" s="106"/>
     </row>
@@ -7493,7 +7643,7 @@
       </c>
       <c r="B74">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C74" s="98" t="s">
         <v>650</v>
@@ -7503,7 +7653,7 @@
       </c>
       <c r="E74" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999068M</v>
+        <v>110101068M</v>
       </c>
       <c r="I74" s="106"/>
     </row>
@@ -7513,7 +7663,7 @@
       </c>
       <c r="B75">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C75" s="98" t="s">
         <v>651</v>
@@ -7523,7 +7673,7 @@
       </c>
       <c r="E75" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999069N</v>
+        <v>110101069N</v>
       </c>
       <c r="I75" s="106"/>
     </row>
@@ -7533,7 +7683,7 @@
       </c>
       <c r="B76">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C76" s="98" t="s">
         <v>652</v>
@@ -7543,7 +7693,7 @@
       </c>
       <c r="E76" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999070R</v>
+        <v>110101070R</v>
       </c>
       <c r="I76" s="106"/>
     </row>
@@ -7553,7 +7703,7 @@
       </c>
       <c r="B77">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C77" s="98" t="s">
         <v>653</v>
@@ -7563,7 +7713,7 @@
       </c>
       <c r="E77" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999071V</v>
+        <v>110101071V</v>
       </c>
       <c r="I77" s="106"/>
     </row>
@@ -7573,7 +7723,7 @@
       </c>
       <c r="B78">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C78" s="98" t="s">
         <v>654</v>
@@ -7583,7 +7733,7 @@
       </c>
       <c r="E78" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999072X</v>
+        <v>110101072X</v>
       </c>
       <c r="I78" s="106"/>
     </row>
@@ -7593,7 +7743,7 @@
       </c>
       <c r="B79">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C79" s="98" t="s">
         <v>655</v>
@@ -7603,7 +7753,7 @@
       </c>
       <c r="E79" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999073A</v>
+        <v>110101073A</v>
       </c>
       <c r="I79" s="106"/>
     </row>
@@ -7613,7 +7763,7 @@
       </c>
       <c r="B80">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C80" s="98" t="s">
         <v>656</v>
@@ -7623,7 +7773,7 @@
       </c>
       <c r="E80" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999074H</v>
+        <v>110101074H</v>
       </c>
       <c r="I80" s="106"/>
     </row>
@@ -7633,7 +7783,7 @@
       </c>
       <c r="B81">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C81" s="98" t="s">
         <v>657</v>
@@ -7643,7 +7793,7 @@
       </c>
       <c r="E81" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999075K</v>
+        <v>110101075K</v>
       </c>
       <c r="I81" s="106"/>
     </row>
@@ -7653,7 +7803,7 @@
       </c>
       <c r="B82">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C82" s="98" t="s">
         <v>658</v>
@@ -7663,7 +7813,7 @@
       </c>
       <c r="E82" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999076M</v>
+        <v>110101076M</v>
       </c>
       <c r="I82" s="106"/>
     </row>
@@ -7673,7 +7823,7 @@
       </c>
       <c r="B83">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C83" s="98" t="s">
         <v>659</v>
@@ -7683,7 +7833,7 @@
       </c>
       <c r="E83" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999077N</v>
+        <v>110101077N</v>
       </c>
       <c r="I83" s="106"/>
     </row>
@@ -7693,7 +7843,7 @@
       </c>
       <c r="B84">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C84" s="98" t="s">
         <v>660</v>
@@ -7703,7 +7853,7 @@
       </c>
       <c r="E84" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999078R</v>
+        <v>110101078R</v>
       </c>
       <c r="I84" s="106"/>
     </row>
@@ -7713,7 +7863,7 @@
       </c>
       <c r="B85">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C85" s="98" t="s">
         <v>661</v>
@@ -7723,7 +7873,7 @@
       </c>
       <c r="E85" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999079V</v>
+        <v>110101079V</v>
       </c>
       <c r="I85" s="106"/>
     </row>
@@ -7733,7 +7883,7 @@
       </c>
       <c r="B86">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C86" s="98" t="s">
         <v>662</v>
@@ -7743,7 +7893,7 @@
       </c>
       <c r="E86" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999080X</v>
+        <v>110101080X</v>
       </c>
       <c r="I86" s="106"/>
     </row>
@@ -7753,7 +7903,7 @@
       </c>
       <c r="B87">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C87" s="98" t="s">
         <v>663</v>
@@ -7763,7 +7913,7 @@
       </c>
       <c r="E87" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999081A</v>
+        <v>110101081A</v>
       </c>
       <c r="I87" s="106"/>
     </row>
@@ -7773,7 +7923,7 @@
       </c>
       <c r="B88">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C88" s="98" t="s">
         <v>664</v>
@@ -7783,7 +7933,7 @@
       </c>
       <c r="E88" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999082H</v>
+        <v>110101082H</v>
       </c>
       <c r="I88" s="106"/>
     </row>
@@ -7793,7 +7943,7 @@
       </c>
       <c r="B89">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C89" s="98" t="s">
         <v>665</v>
@@ -7803,7 +7953,7 @@
       </c>
       <c r="E89" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999083K</v>
+        <v>110101083K</v>
       </c>
       <c r="I89" s="106"/>
     </row>
@@ -7813,7 +7963,7 @@
       </c>
       <c r="B90">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C90" s="98" t="s">
         <v>666</v>
@@ -7823,7 +7973,7 @@
       </c>
       <c r="E90" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999084M</v>
+        <v>110101084M</v>
       </c>
       <c r="I90" s="106"/>
     </row>
@@ -7833,7 +7983,7 @@
       </c>
       <c r="B91">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C91" s="98" t="s">
         <v>667</v>
@@ -7843,7 +7993,7 @@
       </c>
       <c r="E91" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999085N</v>
+        <v>110101085N</v>
       </c>
       <c r="I91" s="106"/>
     </row>
@@ -7853,7 +8003,7 @@
       </c>
       <c r="B92">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C92" s="98" t="s">
         <v>668</v>
@@ -7863,7 +8013,7 @@
       </c>
       <c r="E92" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999086R</v>
+        <v>110101086R</v>
       </c>
       <c r="I92" s="106"/>
     </row>
@@ -7873,7 +8023,7 @@
       </c>
       <c r="B93">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C93" s="98" t="s">
         <v>669</v>
@@ -7883,7 +8033,7 @@
       </c>
       <c r="E93" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999087V</v>
+        <v>110101087V</v>
       </c>
       <c r="I93" s="106"/>
     </row>
@@ -7893,7 +8043,7 @@
       </c>
       <c r="B94">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C94" s="98" t="s">
         <v>670</v>
@@ -7903,7 +8053,7 @@
       </c>
       <c r="E94" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999088X</v>
+        <v>110101088X</v>
       </c>
       <c r="I94" s="106"/>
     </row>
@@ -7913,7 +8063,7 @@
       </c>
       <c r="B95">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C95" s="98" t="s">
         <v>671</v>
@@ -7923,7 +8073,7 @@
       </c>
       <c r="E95" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999089A</v>
+        <v>110101089A</v>
       </c>
       <c r="I95" s="106"/>
     </row>
@@ -7933,7 +8083,7 @@
       </c>
       <c r="B96">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C96" s="98" t="s">
         <v>672</v>
@@ -7943,7 +8093,7 @@
       </c>
       <c r="E96" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999090H</v>
+        <v>110101090H</v>
       </c>
       <c r="I96" s="106"/>
     </row>
@@ -7953,7 +8103,7 @@
       </c>
       <c r="B97">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C97" s="98" t="s">
         <v>673</v>
@@ -7963,7 +8113,7 @@
       </c>
       <c r="E97" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999091K</v>
+        <v>110101091K</v>
       </c>
       <c r="I97" s="106"/>
     </row>
@@ -7973,7 +8123,7 @@
       </c>
       <c r="B98">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C98" s="98" t="s">
         <v>674</v>
@@ -7983,7 +8133,7 @@
       </c>
       <c r="E98" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999092M</v>
+        <v>110101092M</v>
       </c>
       <c r="I98" s="106"/>
     </row>
@@ -7993,7 +8143,7 @@
       </c>
       <c r="B99">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C99" s="98" t="s">
         <v>675</v>
@@ -8003,7 +8153,7 @@
       </c>
       <c r="E99" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999093N</v>
+        <v>110101093N</v>
       </c>
       <c r="I99" s="106"/>
     </row>
@@ -8013,7 +8163,7 @@
       </c>
       <c r="B100">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C100" s="98" t="s">
         <v>676</v>
@@ -8023,7 +8173,7 @@
       </c>
       <c r="E100" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999094R</v>
+        <v>110101094R</v>
       </c>
       <c r="I100" s="106"/>
     </row>
@@ -8033,7 +8183,7 @@
       </c>
       <c r="B101">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C101" s="98" t="s">
         <v>677</v>
@@ -8043,7 +8193,7 @@
       </c>
       <c r="E101" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999095V</v>
+        <v>110101095V</v>
       </c>
       <c r="I101" s="106"/>
     </row>
@@ -8053,7 +8203,7 @@
       </c>
       <c r="B102">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C102" s="98" t="s">
         <v>678</v>
@@ -8063,7 +8213,7 @@
       </c>
       <c r="E102" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999096X</v>
+        <v>110101096X</v>
       </c>
       <c r="I102" s="106"/>
     </row>
@@ -8073,7 +8223,7 @@
       </c>
       <c r="B103">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C103" s="98" t="s">
         <v>679</v>
@@ -8083,7 +8233,7 @@
       </c>
       <c r="E103" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999097A</v>
+        <v>110101097A</v>
       </c>
       <c r="I103" s="106"/>
     </row>
@@ -8093,7 +8243,7 @@
       </c>
       <c r="B104">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C104" s="98" t="s">
         <v>680</v>
@@ -8103,7 +8253,7 @@
       </c>
       <c r="E104" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999098H</v>
+        <v>110101098H</v>
       </c>
       <c r="I104" s="106"/>
     </row>
@@ -8113,7 +8263,7 @@
       </c>
       <c r="B105">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C105" s="98" t="s">
         <v>681</v>
@@ -8123,7 +8273,7 @@
       </c>
       <c r="E105" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999099K</v>
+        <v>110101099K</v>
       </c>
       <c r="I105" s="106"/>
     </row>
@@ -8133,7 +8283,7 @@
       </c>
       <c r="B106">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C106" s="98" t="s">
         <v>682</v>
@@ -8143,7 +8293,7 @@
       </c>
       <c r="E106" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999100M</v>
+        <v>110101100M</v>
       </c>
       <c r="I106" s="106"/>
     </row>
@@ -8153,7 +8303,7 @@
       </c>
       <c r="B107">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C107" s="98" t="s">
         <v>683</v>
@@ -8163,7 +8313,7 @@
       </c>
       <c r="E107" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999101N</v>
+        <v>110101101N</v>
       </c>
       <c r="I107" s="106"/>
     </row>
@@ -8173,7 +8323,7 @@
       </c>
       <c r="B108">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C108" s="98" t="s">
         <v>684</v>
@@ -8183,7 +8333,7 @@
       </c>
       <c r="E108" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999102R</v>
+        <v>110101102R</v>
       </c>
       <c r="I108" s="106"/>
     </row>
@@ -8193,7 +8343,7 @@
       </c>
       <c r="B109">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C109" s="98" t="s">
         <v>685</v>
@@ -8203,7 +8353,7 @@
       </c>
       <c r="E109" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999103V</v>
+        <v>110101103V</v>
       </c>
       <c r="I109" s="106"/>
     </row>
@@ -8213,7 +8363,7 @@
       </c>
       <c r="B110">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C110" s="98" t="s">
         <v>686</v>
@@ -8223,7 +8373,7 @@
       </c>
       <c r="E110" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999104X</v>
+        <v>110101104X</v>
       </c>
       <c r="I110" s="106"/>
     </row>
@@ -8233,7 +8383,7 @@
       </c>
       <c r="B111">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C111" s="98" t="s">
         <v>687</v>
@@ -8243,7 +8393,7 @@
       </c>
       <c r="E111" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999105A</v>
+        <v>110101105A</v>
       </c>
       <c r="I111" s="106"/>
     </row>
@@ -8253,7 +8403,7 @@
       </c>
       <c r="B112">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C112" s="98" t="s">
         <v>688</v>
@@ -8263,7 +8413,7 @@
       </c>
       <c r="E112" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999106H</v>
+        <v>110101106H</v>
       </c>
       <c r="I112" s="106"/>
     </row>
@@ -8273,7 +8423,7 @@
       </c>
       <c r="B113">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C113" s="98" t="s">
         <v>689</v>
@@ -8283,7 +8433,7 @@
       </c>
       <c r="E113" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999107K</v>
+        <v>110101107K</v>
       </c>
       <c r="I113" s="106"/>
     </row>
@@ -8293,7 +8443,7 @@
       </c>
       <c r="B114">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C114" s="98" t="s">
         <v>690</v>
@@ -8303,7 +8453,7 @@
       </c>
       <c r="E114" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999108M</v>
+        <v>110101108M</v>
       </c>
       <c r="I114" s="106"/>
     </row>
@@ -8313,7 +8463,7 @@
       </c>
       <c r="B115">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C115" s="98" t="s">
         <v>691</v>
@@ -8323,7 +8473,7 @@
       </c>
       <c r="E115" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999109N</v>
+        <v>110101109N</v>
       </c>
       <c r="I115" s="106"/>
     </row>
@@ -8333,7 +8483,7 @@
       </c>
       <c r="B116">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C116" s="98" t="s">
         <v>692</v>
@@ -8343,7 +8493,7 @@
       </c>
       <c r="E116" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999110R</v>
+        <v>110101110R</v>
       </c>
       <c r="I116" s="106"/>
     </row>
@@ -8353,7 +8503,7 @@
       </c>
       <c r="B117">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C117" s="98" t="s">
         <v>693</v>
@@ -8363,7 +8513,7 @@
       </c>
       <c r="E117" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999111V</v>
+        <v>110101111V</v>
       </c>
       <c r="I117" s="106"/>
     </row>
@@ -8373,7 +8523,7 @@
       </c>
       <c r="B118">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C118" s="98" t="s">
         <v>694</v>
@@ -8383,7 +8533,7 @@
       </c>
       <c r="E118" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999112X</v>
+        <v>110101112X</v>
       </c>
       <c r="I118" s="106"/>
     </row>
@@ -8393,7 +8543,7 @@
       </c>
       <c r="B119">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C119" s="98" t="s">
         <v>695</v>
@@ -8403,7 +8553,7 @@
       </c>
       <c r="E119" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999113A</v>
+        <v>110101113A</v>
       </c>
       <c r="I119" s="106"/>
     </row>
@@ -8413,7 +8563,7 @@
       </c>
       <c r="B120">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C120" s="98" t="s">
         <v>696</v>
@@ -8423,7 +8573,7 @@
       </c>
       <c r="E120" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999114H</v>
+        <v>110101114H</v>
       </c>
       <c r="I120" s="106"/>
     </row>
@@ -8433,7 +8583,7 @@
       </c>
       <c r="B121">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C121" s="98" t="s">
         <v>697</v>
@@ -8443,7 +8593,7 @@
       </c>
       <c r="E121" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999115K</v>
+        <v>110101115K</v>
       </c>
       <c r="I121" s="106"/>
     </row>
@@ -8453,7 +8603,7 @@
       </c>
       <c r="B122">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C122" s="98" t="s">
         <v>698</v>
@@ -8463,7 +8613,7 @@
       </c>
       <c r="E122" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999116M</v>
+        <v>110101116M</v>
       </c>
       <c r="I122" s="106"/>
     </row>
@@ -8473,7 +8623,7 @@
       </c>
       <c r="B123">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C123" s="98" t="s">
         <v>699</v>
@@ -8483,7 +8633,7 @@
       </c>
       <c r="E123" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999117N</v>
+        <v>110101117N</v>
       </c>
       <c r="I123" s="106"/>
     </row>
@@ -8493,7 +8643,7 @@
       </c>
       <c r="B124">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C124" s="98" t="s">
         <v>700</v>
@@ -8503,7 +8653,7 @@
       </c>
       <c r="E124" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999118R</v>
+        <v>110101118R</v>
       </c>
       <c r="I124" s="106"/>
     </row>
@@ -8513,7 +8663,7 @@
       </c>
       <c r="B125">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C125" s="98" t="s">
         <v>701</v>
@@ -8523,7 +8673,7 @@
       </c>
       <c r="E125" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999119V</v>
+        <v>110101119V</v>
       </c>
       <c r="I125" s="106"/>
     </row>
@@ -8533,7 +8683,7 @@
       </c>
       <c r="B126">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C126" s="98" t="s">
         <v>702</v>
@@ -8543,7 +8693,7 @@
       </c>
       <c r="E126" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999120X</v>
+        <v>110101120X</v>
       </c>
       <c r="I126" s="106"/>
     </row>
@@ -8553,7 +8703,7 @@
       </c>
       <c r="B127">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C127" s="98" t="s">
         <v>703</v>
@@ -8563,7 +8713,7 @@
       </c>
       <c r="E127" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999121A</v>
+        <v>110101121A</v>
       </c>
       <c r="I127" s="106"/>
     </row>
@@ -8573,7 +8723,7 @@
       </c>
       <c r="B128">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C128" s="98" t="s">
         <v>704</v>
@@ -8583,7 +8733,7 @@
       </c>
       <c r="E128" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999122H</v>
+        <v>110101122H</v>
       </c>
       <c r="I128" s="106"/>
     </row>
@@ -8593,7 +8743,7 @@
       </c>
       <c r="B129">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C129" s="98" t="s">
         <v>705</v>
@@ -8603,7 +8753,7 @@
       </c>
       <c r="E129" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999123K</v>
+        <v>110101123K</v>
       </c>
       <c r="I129" s="106"/>
     </row>
@@ -8613,7 +8763,7 @@
       </c>
       <c r="B130">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C130" s="98" t="s">
         <v>706</v>
@@ -8623,7 +8773,7 @@
       </c>
       <c r="E130" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999124M</v>
+        <v>110101124M</v>
       </c>
       <c r="I130" s="106"/>
     </row>
@@ -8633,7 +8783,7 @@
       </c>
       <c r="B131">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C131" s="98" t="s">
         <v>707</v>
@@ -8643,7 +8793,7 @@
       </c>
       <c r="E131" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999125N</v>
+        <v>110101125N</v>
       </c>
       <c r="I131" s="106"/>
     </row>
@@ -8653,7 +8803,7 @@
       </c>
       <c r="B132">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C132" s="98" t="s">
         <v>708</v>
@@ -8663,7 +8813,7 @@
       </c>
       <c r="E132" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999126R</v>
+        <v>110101126R</v>
       </c>
       <c r="I132" s="106"/>
     </row>
@@ -8673,7 +8823,7 @@
       </c>
       <c r="B133">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C133" s="98" t="s">
         <v>709</v>
@@ -8683,7 +8833,7 @@
       </c>
       <c r="E133" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999127V</v>
+        <v>110101127V</v>
       </c>
       <c r="I133" s="106"/>
     </row>
@@ -8693,7 +8843,7 @@
       </c>
       <c r="B134">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C134" s="98" t="s">
         <v>710</v>
@@ -8703,7 +8853,7 @@
       </c>
       <c r="E134" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999128X</v>
+        <v>110101128X</v>
       </c>
       <c r="I134" s="106"/>
     </row>
@@ -8713,7 +8863,7 @@
       </c>
       <c r="B135">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C135" s="98" t="s">
         <v>711</v>
@@ -8723,7 +8873,7 @@
       </c>
       <c r="E135" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999129A</v>
+        <v>110101129A</v>
       </c>
       <c r="I135" s="106"/>
     </row>
@@ -8733,7 +8883,7 @@
       </c>
       <c r="B136">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C136" s="98" t="s">
         <v>712</v>
@@ -8743,7 +8893,7 @@
       </c>
       <c r="E136" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999130H</v>
+        <v>110101130H</v>
       </c>
       <c r="I136" s="106"/>
     </row>
@@ -8753,7 +8903,7 @@
       </c>
       <c r="B137">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C137" s="98" t="s">
         <v>713</v>
@@ -8763,7 +8913,7 @@
       </c>
       <c r="E137" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999131K</v>
+        <v>110101131K</v>
       </c>
       <c r="I137" s="106"/>
     </row>
@@ -8773,7 +8923,7 @@
       </c>
       <c r="B138">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C138" s="98" t="s">
         <v>714</v>
@@ -8783,7 +8933,7 @@
       </c>
       <c r="E138" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999132M</v>
+        <v>110101132M</v>
       </c>
       <c r="I138" s="106"/>
     </row>
@@ -8793,7 +8943,7 @@
       </c>
       <c r="B139">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C139" s="98" t="s">
         <v>715</v>
@@ -8803,7 +8953,7 @@
       </c>
       <c r="E139" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999133N</v>
+        <v>110101133N</v>
       </c>
       <c r="I139" s="106"/>
     </row>
@@ -8813,7 +8963,7 @@
       </c>
       <c r="B140">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C140" s="98" t="s">
         <v>716</v>
@@ -8823,7 +8973,7 @@
       </c>
       <c r="E140" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999134R</v>
+        <v>110101134R</v>
       </c>
       <c r="I140" s="106"/>
     </row>
@@ -8833,7 +8983,7 @@
       </c>
       <c r="B141">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C141" s="98" t="s">
         <v>717</v>
@@ -8843,7 +8993,7 @@
       </c>
       <c r="E141" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999135V</v>
+        <v>110101135V</v>
       </c>
       <c r="I141" s="106"/>
     </row>
@@ -8853,7 +9003,7 @@
       </c>
       <c r="B142">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C142" s="98" t="s">
         <v>718</v>
@@ -8863,7 +9013,7 @@
       </c>
       <c r="E142" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999136X</v>
+        <v>110101136X</v>
       </c>
       <c r="I142" s="106"/>
     </row>
@@ -8873,7 +9023,7 @@
       </c>
       <c r="B143">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C143" s="98" t="s">
         <v>719</v>
@@ -8883,7 +9033,7 @@
       </c>
       <c r="E143" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999137A</v>
+        <v>110101137A</v>
       </c>
       <c r="I143" s="106"/>
     </row>
@@ -8893,7 +9043,7 @@
       </c>
       <c r="B144">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C144" s="98" t="s">
         <v>720</v>
@@ -8903,7 +9053,7 @@
       </c>
       <c r="E144" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999138H</v>
+        <v>110101138H</v>
       </c>
       <c r="I144" s="106"/>
     </row>
@@ -8913,7 +9063,7 @@
       </c>
       <c r="B145">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C145" s="98" t="s">
         <v>721</v>
@@ -8923,7 +9073,7 @@
       </c>
       <c r="E145" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999139K</v>
+        <v>110101139K</v>
       </c>
       <c r="I145" s="106"/>
     </row>
@@ -8933,7 +9083,7 @@
       </c>
       <c r="B146">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C146" s="98" t="s">
         <v>722</v>
@@ -8943,7 +9093,7 @@
       </c>
       <c r="E146" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999140M</v>
+        <v>110101140M</v>
       </c>
       <c r="I146" s="106"/>
     </row>
@@ -8953,7 +9103,7 @@
       </c>
       <c r="B147">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C147" s="98" t="s">
         <v>723</v>
@@ -8963,7 +9113,7 @@
       </c>
       <c r="E147" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999141N</v>
+        <v>110101141N</v>
       </c>
       <c r="I147" s="106"/>
     </row>
@@ -8973,7 +9123,7 @@
       </c>
       <c r="B148">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C148" s="98" t="s">
         <v>724</v>
@@ -8983,7 +9133,7 @@
       </c>
       <c r="E148" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999142R</v>
+        <v>110101142R</v>
       </c>
       <c r="I148" s="106"/>
     </row>
@@ -8993,7 +9143,7 @@
       </c>
       <c r="B149">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C149" s="98" t="s">
         <v>725</v>
@@ -9003,7 +9153,7 @@
       </c>
       <c r="E149" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999143V</v>
+        <v>110101143V</v>
       </c>
       <c r="I149" s="106"/>
     </row>
@@ -9013,7 +9163,7 @@
       </c>
       <c r="B150">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C150" s="98" t="s">
         <v>726</v>
@@ -9023,7 +9173,7 @@
       </c>
       <c r="E150" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999144X</v>
+        <v>110101144X</v>
       </c>
       <c r="I150" s="106"/>
     </row>
@@ -9033,7 +9183,7 @@
       </c>
       <c r="B151">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C151" s="98" t="s">
         <v>727</v>
@@ -9043,7 +9193,7 @@
       </c>
       <c r="E151" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999145A</v>
+        <v>110101145A</v>
       </c>
       <c r="I151" s="106"/>
     </row>
@@ -9053,7 +9203,7 @@
       </c>
       <c r="B152">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C152" s="98" t="s">
         <v>728</v>
@@ -9063,7 +9213,7 @@
       </c>
       <c r="E152" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999146H</v>
+        <v>110101146H</v>
       </c>
       <c r="I152" s="106"/>
     </row>
@@ -9073,7 +9223,7 @@
       </c>
       <c r="B153">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C153" s="98" t="s">
         <v>729</v>
@@ -9083,7 +9233,7 @@
       </c>
       <c r="E153" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999147K</v>
+        <v>110101147K</v>
       </c>
       <c r="I153" s="106"/>
     </row>
@@ -9093,7 +9243,7 @@
       </c>
       <c r="B154">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C154" s="98" t="s">
         <v>730</v>
@@ -9103,7 +9253,7 @@
       </c>
       <c r="E154" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999148M</v>
+        <v>110101148M</v>
       </c>
       <c r="I154" s="106"/>
     </row>
@@ -9113,7 +9263,7 @@
       </c>
       <c r="B155">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C155" s="98" t="s">
         <v>731</v>
@@ -9123,7 +9273,7 @@
       </c>
       <c r="E155" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999149N</v>
+        <v>110101149N</v>
       </c>
       <c r="I155" s="106"/>
     </row>
@@ -9133,7 +9283,7 @@
       </c>
       <c r="B156">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C156" s="98" t="s">
         <v>732</v>
@@ -9143,7 +9293,7 @@
       </c>
       <c r="E156" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999150R</v>
+        <v>110101150R</v>
       </c>
       <c r="I156" s="106"/>
     </row>
@@ -9153,7 +9303,7 @@
       </c>
       <c r="B157">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C157" s="98" t="s">
         <v>733</v>
@@ -9163,7 +9313,7 @@
       </c>
       <c r="E157" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999151V</v>
+        <v>110101151V</v>
       </c>
       <c r="I157" s="106"/>
     </row>
@@ -9173,7 +9323,7 @@
       </c>
       <c r="B158">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C158" s="98" t="s">
         <v>734</v>
@@ -9183,7 +9333,7 @@
       </c>
       <c r="E158" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999152X</v>
+        <v>110101152X</v>
       </c>
       <c r="I158" s="106"/>
     </row>
@@ -9193,7 +9343,7 @@
       </c>
       <c r="B159">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C159" s="98" t="s">
         <v>735</v>
@@ -9203,7 +9353,7 @@
       </c>
       <c r="E159" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999153A</v>
+        <v>110101153A</v>
       </c>
       <c r="I159" s="106"/>
     </row>
@@ -9213,7 +9363,7 @@
       </c>
       <c r="B160">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C160" s="98" t="s">
         <v>736</v>
@@ -9223,7 +9373,7 @@
       </c>
       <c r="E160" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999154H</v>
+        <v>110101154H</v>
       </c>
       <c r="I160" s="106"/>
     </row>
@@ -9233,7 +9383,7 @@
       </c>
       <c r="B161">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C161" s="98" t="s">
         <v>737</v>
@@ -9243,7 +9393,7 @@
       </c>
       <c r="E161" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999155K</v>
+        <v>110101155K</v>
       </c>
       <c r="I161" s="106"/>
     </row>
@@ -9253,7 +9403,7 @@
       </c>
       <c r="B162">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C162" s="98" t="s">
         <v>738</v>
@@ -9263,7 +9413,7 @@
       </c>
       <c r="E162" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999156M</v>
+        <v>110101156M</v>
       </c>
       <c r="I162" s="106"/>
     </row>
@@ -9273,7 +9423,7 @@
       </c>
       <c r="B163">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C163" s="98" t="s">
         <v>739</v>
@@ -9283,7 +9433,7 @@
       </c>
       <c r="E163" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999157N</v>
+        <v>110101157N</v>
       </c>
       <c r="I163" s="106"/>
     </row>
@@ -9293,7 +9443,7 @@
       </c>
       <c r="B164">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C164" s="98" t="s">
         <v>740</v>
@@ -9303,7 +9453,7 @@
       </c>
       <c r="E164" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999158R</v>
+        <v>110101158R</v>
       </c>
       <c r="I164" s="106"/>
     </row>
@@ -9313,7 +9463,7 @@
       </c>
       <c r="B165">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C165" s="98" t="s">
         <v>741</v>
@@ -9323,7 +9473,7 @@
       </c>
       <c r="E165" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999159V</v>
+        <v>110101159V</v>
       </c>
       <c r="I165" s="106"/>
     </row>
@@ -9333,7 +9483,7 @@
       </c>
       <c r="B166">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C166" s="98" t="s">
         <v>742</v>
@@ -9343,7 +9493,7 @@
       </c>
       <c r="E166" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999160X</v>
+        <v>110101160X</v>
       </c>
       <c r="I166" s="106"/>
     </row>
@@ -9353,7 +9503,7 @@
       </c>
       <c r="B167">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C167" s="98" t="s">
         <v>743</v>
@@ -9363,7 +9513,7 @@
       </c>
       <c r="E167" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999161A</v>
+        <v>110101161A</v>
       </c>
       <c r="I167" s="106"/>
     </row>
@@ -9373,7 +9523,7 @@
       </c>
       <c r="B168">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C168" s="98" t="s">
         <v>744</v>
@@ -9383,7 +9533,7 @@
       </c>
       <c r="E168" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999162H</v>
+        <v>110101162H</v>
       </c>
       <c r="I168" s="106"/>
     </row>
@@ -9393,7 +9543,7 @@
       </c>
       <c r="B169">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C169" s="98" t="s">
         <v>745</v>
@@ -9403,7 +9553,7 @@
       </c>
       <c r="E169" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999163K</v>
+        <v>110101163K</v>
       </c>
       <c r="I169" s="106"/>
     </row>
@@ -9413,7 +9563,7 @@
       </c>
       <c r="B170">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C170" s="98" t="s">
         <v>746</v>
@@ -9423,7 +9573,7 @@
       </c>
       <c r="E170" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999164M</v>
+        <v>110101164M</v>
       </c>
       <c r="I170" s="106"/>
     </row>
@@ -9433,7 +9583,7 @@
       </c>
       <c r="B171">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C171" s="98" t="s">
         <v>747</v>
@@ -9443,7 +9593,7 @@
       </c>
       <c r="E171" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999165N</v>
+        <v>110101165N</v>
       </c>
       <c r="I171" s="106"/>
     </row>
@@ -9453,7 +9603,7 @@
       </c>
       <c r="B172">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C172" s="98" t="s">
         <v>748</v>
@@ -9463,7 +9613,7 @@
       </c>
       <c r="E172" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999166R</v>
+        <v>110101166R</v>
       </c>
       <c r="I172" s="106"/>
     </row>
@@ -9473,7 +9623,7 @@
       </c>
       <c r="B173">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C173" s="98" t="s">
         <v>749</v>
@@ -9483,7 +9633,7 @@
       </c>
       <c r="E173" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999167V</v>
+        <v>110101167V</v>
       </c>
       <c r="I173" s="106"/>
     </row>
@@ -9493,7 +9643,7 @@
       </c>
       <c r="B174">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C174" s="98" t="s">
         <v>750</v>
@@ -9503,7 +9653,7 @@
       </c>
       <c r="E174" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999168X</v>
+        <v>110101168X</v>
       </c>
       <c r="I174" s="106"/>
     </row>
@@ -9513,7 +9663,7 @@
       </c>
       <c r="B175">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C175" s="98" t="s">
         <v>751</v>
@@ -9523,7 +9673,7 @@
       </c>
       <c r="E175" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999169A</v>
+        <v>110101169A</v>
       </c>
       <c r="I175" s="106"/>
     </row>
@@ -9533,7 +9683,7 @@
       </c>
       <c r="B176">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C176" s="98" t="s">
         <v>752</v>
@@ -9543,7 +9693,7 @@
       </c>
       <c r="E176" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999170H</v>
+        <v>110101170H</v>
       </c>
       <c r="I176" s="106"/>
     </row>
@@ -9553,7 +9703,7 @@
       </c>
       <c r="B177">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C177" s="98" t="s">
         <v>753</v>
@@ -9563,7 +9713,7 @@
       </c>
       <c r="E177" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999171K</v>
+        <v>110101171K</v>
       </c>
       <c r="I177" s="106"/>
     </row>
@@ -9573,7 +9723,7 @@
       </c>
       <c r="B178">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C178" s="98" t="s">
         <v>754</v>
@@ -9583,7 +9733,7 @@
       </c>
       <c r="E178" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999172M</v>
+        <v>110101172M</v>
       </c>
       <c r="I178" s="106"/>
     </row>
@@ -9593,7 +9743,7 @@
       </c>
       <c r="B179">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C179" s="98" t="s">
         <v>755</v>
@@ -9603,7 +9753,7 @@
       </c>
       <c r="E179" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999173N</v>
+        <v>110101173N</v>
       </c>
       <c r="I179" s="106"/>
     </row>
@@ -9613,7 +9763,7 @@
       </c>
       <c r="B180">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C180" s="98" t="s">
         <v>756</v>
@@ -9623,7 +9773,7 @@
       </c>
       <c r="E180" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999174R</v>
+        <v>110101174R</v>
       </c>
       <c r="I180" s="106"/>
     </row>
@@ -9633,7 +9783,7 @@
       </c>
       <c r="B181">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C181" s="98" t="s">
         <v>757</v>
@@ -9643,7 +9793,7 @@
       </c>
       <c r="E181" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999175V</v>
+        <v>110101175V</v>
       </c>
       <c r="I181" s="106"/>
     </row>
@@ -9653,7 +9803,7 @@
       </c>
       <c r="B182">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C182" s="98" t="s">
         <v>758</v>
@@ -9663,7 +9813,7 @@
       </c>
       <c r="E182" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999176X</v>
+        <v>110101176X</v>
       </c>
       <c r="I182" s="106"/>
     </row>
@@ -9673,7 +9823,7 @@
       </c>
       <c r="B183">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C183" s="98" t="s">
         <v>759</v>
@@ -9683,7 +9833,7 @@
       </c>
       <c r="E183" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999177A</v>
+        <v>110101177A</v>
       </c>
       <c r="I183" s="106"/>
     </row>
@@ -9693,7 +9843,7 @@
       </c>
       <c r="B184">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C184" s="98" t="s">
         <v>760</v>
@@ -9703,7 +9853,7 @@
       </c>
       <c r="E184" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999178H</v>
+        <v>110101178H</v>
       </c>
       <c r="I184" s="106"/>
     </row>
@@ -9713,7 +9863,7 @@
       </c>
       <c r="B185">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C185" s="98" t="s">
         <v>761</v>
@@ -9723,7 +9873,7 @@
       </c>
       <c r="E185" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999179K</v>
+        <v>110101179K</v>
       </c>
       <c r="I185" s="106"/>
     </row>
@@ -9733,7 +9883,7 @@
       </c>
       <c r="B186">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C186" s="98" t="s">
         <v>762</v>
@@ -9743,7 +9893,7 @@
       </c>
       <c r="E186" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999180M</v>
+        <v>110101180M</v>
       </c>
       <c r="I186" s="106"/>
     </row>
@@ -9753,7 +9903,7 @@
       </c>
       <c r="B187">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C187" s="98" t="s">
         <v>763</v>
@@ -9763,7 +9913,7 @@
       </c>
       <c r="E187" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999181N</v>
+        <v>110101181N</v>
       </c>
       <c r="I187" s="106"/>
     </row>
@@ -9773,7 +9923,7 @@
       </c>
       <c r="B188">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C188" s="98" t="s">
         <v>764</v>
@@ -9783,7 +9933,7 @@
       </c>
       <c r="E188" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999182R</v>
+        <v>110101182R</v>
       </c>
       <c r="I188" s="106"/>
     </row>
@@ -9793,7 +9943,7 @@
       </c>
       <c r="B189">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C189" s="98" t="s">
         <v>765</v>
@@ -9803,7 +9953,7 @@
       </c>
       <c r="E189" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999183V</v>
+        <v>110101183V</v>
       </c>
       <c r="I189" s="106"/>
     </row>
@@ -9813,7 +9963,7 @@
       </c>
       <c r="B190">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C190" s="98" t="s">
         <v>766</v>
@@ -9823,7 +9973,7 @@
       </c>
       <c r="E190" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999184X</v>
+        <v>110101184X</v>
       </c>
       <c r="I190" s="106"/>
     </row>
@@ -9833,7 +9983,7 @@
       </c>
       <c r="B191">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C191" s="98" t="s">
         <v>767</v>
@@ -9843,7 +9993,7 @@
       </c>
       <c r="E191" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999185A</v>
+        <v>110101185A</v>
       </c>
       <c r="I191" s="106"/>
     </row>
@@ -9853,7 +10003,7 @@
       </c>
       <c r="B192">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C192" s="98" t="s">
         <v>768</v>
@@ -9863,7 +10013,7 @@
       </c>
       <c r="E192" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999186H</v>
+        <v>110101186H</v>
       </c>
       <c r="I192" s="106"/>
     </row>
@@ -9873,7 +10023,7 @@
       </c>
       <c r="B193">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C193" s="98" t="s">
         <v>769</v>
@@ -9883,7 +10033,7 @@
       </c>
       <c r="E193" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999187K</v>
+        <v>110101187K</v>
       </c>
       <c r="I193" s="106"/>
     </row>
@@ -9893,7 +10043,7 @@
       </c>
       <c r="B194">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C194" s="98" t="s">
         <v>770</v>
@@ -9903,7 +10053,7 @@
       </c>
       <c r="E194" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999188M</v>
+        <v>110101188M</v>
       </c>
       <c r="I194" s="106"/>
     </row>
@@ -9913,7 +10063,7 @@
       </c>
       <c r="B195">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C195" s="98" t="s">
         <v>771</v>
@@ -9923,7 +10073,7 @@
       </c>
       <c r="E195" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999189N</v>
+        <v>110101189N</v>
       </c>
       <c r="I195" s="106"/>
     </row>
@@ -9933,7 +10083,7 @@
       </c>
       <c r="B196">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C196" s="98" t="s">
         <v>772</v>
@@ -9943,7 +10093,7 @@
       </c>
       <c r="E196" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999190R</v>
+        <v>110101190R</v>
       </c>
       <c r="I196" s="106"/>
     </row>
@@ -9953,7 +10103,7 @@
       </c>
       <c r="B197">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C197" s="98" t="s">
         <v>773</v>
@@ -9963,7 +10113,7 @@
       </c>
       <c r="E197" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999191V</v>
+        <v>110101191V</v>
       </c>
       <c r="I197" s="106"/>
     </row>
@@ -9973,7 +10123,7 @@
       </c>
       <c r="B198">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C198" s="98" t="s">
         <v>774</v>
@@ -9983,7 +10133,7 @@
       </c>
       <c r="E198" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999192X</v>
+        <v>110101192X</v>
       </c>
       <c r="I198" s="106"/>
     </row>
@@ -9993,7 +10143,7 @@
       </c>
       <c r="B199">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C199" s="98" t="s">
         <v>775</v>
@@ -10003,7 +10153,7 @@
       </c>
       <c r="E199" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999193A</v>
+        <v>110101193A</v>
       </c>
       <c r="I199" s="106"/>
     </row>
@@ -10013,7 +10163,7 @@
       </c>
       <c r="B200">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C200" s="98" t="s">
         <v>776</v>
@@ -10023,7 +10173,7 @@
       </c>
       <c r="E200" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999194H</v>
+        <v>110101194H</v>
       </c>
       <c r="I200" s="106"/>
     </row>
@@ -10033,7 +10183,7 @@
       </c>
       <c r="B201">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C201" s="98" t="s">
         <v>777</v>
@@ -10043,7 +10193,7 @@
       </c>
       <c r="E201" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999195K</v>
+        <v>110101195K</v>
       </c>
       <c r="I201" s="106"/>
     </row>
@@ -10053,7 +10203,7 @@
       </c>
       <c r="B202">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C202" s="98" t="s">
         <v>778</v>
@@ -10063,7 +10213,7 @@
       </c>
       <c r="E202" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999196M</v>
+        <v>110101196M</v>
       </c>
       <c r="I202" s="106"/>
     </row>
@@ -10073,7 +10223,7 @@
       </c>
       <c r="B203">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C203" s="98" t="s">
         <v>779</v>
@@ -10083,7 +10233,7 @@
       </c>
       <c r="E203" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999197N</v>
+        <v>110101197N</v>
       </c>
       <c r="I203" s="106"/>
     </row>
@@ -10093,7 +10243,7 @@
       </c>
       <c r="B204">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C204" s="98" t="s">
         <v>780</v>
@@ -10103,7 +10253,7 @@
       </c>
       <c r="E204" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999198R</v>
+        <v>110101198R</v>
       </c>
       <c r="I204" s="106"/>
     </row>
@@ -10113,7 +10263,7 @@
       </c>
       <c r="B205">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C205" s="98" t="s">
         <v>781</v>
@@ -10123,7 +10273,7 @@
       </c>
       <c r="E205" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999199V</v>
+        <v>110101199V</v>
       </c>
       <c r="I205" s="106"/>
     </row>
@@ -10133,7 +10283,7 @@
       </c>
       <c r="B206">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C206" s="98" t="s">
         <v>782</v>
@@ -10143,7 +10293,7 @@
       </c>
       <c r="E206" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999200X</v>
+        <v>110101200X</v>
       </c>
       <c r="I206" s="106"/>
     </row>
@@ -10153,7 +10303,7 @@
       </c>
       <c r="B207">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C207" s="98" t="s">
         <v>783</v>
@@ -10163,7 +10313,7 @@
       </c>
       <c r="E207" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999201A</v>
+        <v>110101201A</v>
       </c>
       <c r="I207" s="106"/>
     </row>
@@ -10173,7 +10323,7 @@
       </c>
       <c r="B208">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C208" s="98" t="s">
         <v>784</v>
@@ -10183,7 +10333,7 @@
       </c>
       <c r="E208" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999202H</v>
+        <v>110101202H</v>
       </c>
       <c r="I208" s="106"/>
     </row>
@@ -10193,7 +10343,7 @@
       </c>
       <c r="B209">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C209" s="98" t="s">
         <v>785</v>
@@ -10203,7 +10353,7 @@
       </c>
       <c r="E209" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999203K</v>
+        <v>110101203K</v>
       </c>
       <c r="I209" s="106"/>
     </row>
@@ -10213,7 +10363,7 @@
       </c>
       <c r="B210">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C210" s="98" t="s">
         <v>786</v>
@@ -10223,7 +10373,7 @@
       </c>
       <c r="E210" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999204M</v>
+        <v>110101204M</v>
       </c>
       <c r="I210" s="106"/>
     </row>
@@ -10233,7 +10383,7 @@
       </c>
       <c r="B211">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C211" s="98" t="s">
         <v>787</v>
@@ -10243,7 +10393,7 @@
       </c>
       <c r="E211" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999205N</v>
+        <v>110101205N</v>
       </c>
       <c r="I211" s="106"/>
     </row>
@@ -10253,7 +10403,7 @@
       </c>
       <c r="B212">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C212" s="98" t="s">
         <v>788</v>
@@ -10263,7 +10413,7 @@
       </c>
       <c r="E212" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999206R</v>
+        <v>110101206R</v>
       </c>
       <c r="I212" s="106"/>
     </row>
@@ -10273,7 +10423,7 @@
       </c>
       <c r="B213">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C213" s="98" t="s">
         <v>789</v>
@@ -10283,7 +10433,7 @@
       </c>
       <c r="E213" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999207V</v>
+        <v>110101207V</v>
       </c>
       <c r="I213" s="106"/>
     </row>
@@ -10293,7 +10443,7 @@
       </c>
       <c r="B214">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C214" s="98" t="s">
         <v>790</v>
@@ -10303,7 +10453,7 @@
       </c>
       <c r="E214" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999208X</v>
+        <v>110101208X</v>
       </c>
       <c r="I214" s="106"/>
     </row>
@@ -10313,7 +10463,7 @@
       </c>
       <c r="B215">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C215" s="98" t="s">
         <v>791</v>
@@ -10323,7 +10473,7 @@
       </c>
       <c r="E215" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999209A</v>
+        <v>110101209A</v>
       </c>
       <c r="I215" s="106"/>
     </row>
@@ -10333,7 +10483,7 @@
       </c>
       <c r="B216">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C216" s="98" t="s">
         <v>792</v>
@@ -10343,7 +10493,7 @@
       </c>
       <c r="E216" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999210H</v>
+        <v>110101210H</v>
       </c>
       <c r="I216" s="106"/>
     </row>
@@ -10353,7 +10503,7 @@
       </c>
       <c r="B217">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C217" s="98" t="s">
         <v>793</v>
@@ -10363,7 +10513,7 @@
       </c>
       <c r="E217" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999211K</v>
+        <v>110101211K</v>
       </c>
       <c r="I217" s="106"/>
     </row>
@@ -10373,7 +10523,7 @@
       </c>
       <c r="B218">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C218" s="98" t="s">
         <v>794</v>
@@ -10383,7 +10533,7 @@
       </c>
       <c r="E218" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999212M</v>
+        <v>110101212M</v>
       </c>
       <c r="I218" s="106"/>
     </row>
@@ -10393,7 +10543,7 @@
       </c>
       <c r="B219">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C219" s="98" t="s">
         <v>795</v>
@@ -10403,7 +10553,7 @@
       </c>
       <c r="E219" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999213N</v>
+        <v>110101213N</v>
       </c>
       <c r="I219" s="106"/>
     </row>
@@ -10413,7 +10563,7 @@
       </c>
       <c r="B220">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C220" s="98" t="s">
         <v>796</v>
@@ -10423,7 +10573,7 @@
       </c>
       <c r="E220" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999214R</v>
+        <v>110101214R</v>
       </c>
       <c r="I220" s="106"/>
     </row>
@@ -10433,7 +10583,7 @@
       </c>
       <c r="B221">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C221" s="98" t="s">
         <v>797</v>
@@ -10443,7 +10593,7 @@
       </c>
       <c r="E221" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999215V</v>
+        <v>110101215V</v>
       </c>
       <c r="I221" s="106"/>
     </row>
@@ -10453,7 +10603,7 @@
       </c>
       <c r="B222">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C222" s="98" t="s">
         <v>798</v>
@@ -10463,7 +10613,7 @@
       </c>
       <c r="E222" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999216X</v>
+        <v>110101216X</v>
       </c>
       <c r="I222" s="106"/>
     </row>
@@ -10473,7 +10623,7 @@
       </c>
       <c r="B223">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C223" s="98" t="s">
         <v>799</v>
@@ -10483,7 +10633,7 @@
       </c>
       <c r="E223" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999217A</v>
+        <v>110101217A</v>
       </c>
       <c r="I223" s="106"/>
     </row>
@@ -10493,7 +10643,7 @@
       </c>
       <c r="B224">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C224" s="98" t="s">
         <v>800</v>
@@ -10503,7 +10653,7 @@
       </c>
       <c r="E224" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999218H</v>
+        <v>110101218H</v>
       </c>
       <c r="I224" s="106"/>
     </row>
@@ -10513,7 +10663,7 @@
       </c>
       <c r="B225">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C225" s="98" t="s">
         <v>801</v>
@@ -10523,7 +10673,7 @@
       </c>
       <c r="E225" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999219K</v>
+        <v>110101219K</v>
       </c>
       <c r="I225" s="106"/>
     </row>
@@ -10533,7 +10683,7 @@
       </c>
       <c r="B226">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C226" s="98" t="s">
         <v>802</v>
@@ -10543,7 +10693,7 @@
       </c>
       <c r="E226" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999220M</v>
+        <v>110101220M</v>
       </c>
       <c r="I226" s="106"/>
     </row>
@@ -10553,7 +10703,7 @@
       </c>
       <c r="B227">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C227" s="98" t="s">
         <v>803</v>
@@ -10563,7 +10713,7 @@
       </c>
       <c r="E227" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999221N</v>
+        <v>110101221N</v>
       </c>
       <c r="I227" s="106"/>
     </row>
@@ -10573,7 +10723,7 @@
       </c>
       <c r="B228">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C228" s="98" t="s">
         <v>804</v>
@@ -10583,7 +10733,7 @@
       </c>
       <c r="E228" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999222R</v>
+        <v>110101222R</v>
       </c>
       <c r="I228" s="106"/>
     </row>
@@ -10593,7 +10743,7 @@
       </c>
       <c r="B229">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C229" s="98" t="s">
         <v>805</v>
@@ -10603,7 +10753,7 @@
       </c>
       <c r="E229" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999223V</v>
+        <v>110101223V</v>
       </c>
       <c r="I229" s="106"/>
     </row>
@@ -10613,7 +10763,7 @@
       </c>
       <c r="B230">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C230" s="98" t="s">
         <v>806</v>
@@ -10623,7 +10773,7 @@
       </c>
       <c r="E230" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999224X</v>
+        <v>110101224X</v>
       </c>
       <c r="I230" s="106"/>
     </row>
@@ -10633,7 +10783,7 @@
       </c>
       <c r="B231">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C231" s="98" t="s">
         <v>807</v>
@@ -10643,7 +10793,7 @@
       </c>
       <c r="E231" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999225A</v>
+        <v>110101225A</v>
       </c>
       <c r="I231" s="106"/>
     </row>
@@ -10653,7 +10803,7 @@
       </c>
       <c r="B232">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C232" s="98" t="s">
         <v>808</v>
@@ -10663,7 +10813,7 @@
       </c>
       <c r="E232" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999226H</v>
+        <v>110101226H</v>
       </c>
       <c r="I232" s="106"/>
     </row>
@@ -10673,7 +10823,7 @@
       </c>
       <c r="B233">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C233" s="98" t="s">
         <v>809</v>
@@ -10683,7 +10833,7 @@
       </c>
       <c r="E233" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999227K</v>
+        <v>110101227K</v>
       </c>
       <c r="I233" s="106"/>
     </row>
@@ -10693,7 +10843,7 @@
       </c>
       <c r="B234">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C234" s="98" t="s">
         <v>810</v>
@@ -10703,7 +10853,7 @@
       </c>
       <c r="E234" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999228M</v>
+        <v>110101228M</v>
       </c>
       <c r="I234" s="106"/>
     </row>
@@ -10713,7 +10863,7 @@
       </c>
       <c r="B235">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C235" s="98" t="s">
         <v>811</v>
@@ -10723,7 +10873,7 @@
       </c>
       <c r="E235" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999229N</v>
+        <v>110101229N</v>
       </c>
       <c r="I235" s="106"/>
     </row>
@@ -10733,7 +10883,7 @@
       </c>
       <c r="B236">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C236" s="98" t="s">
         <v>812</v>
@@ -10743,7 +10893,7 @@
       </c>
       <c r="E236" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999230R</v>
+        <v>110101230R</v>
       </c>
       <c r="I236" s="106"/>
     </row>
@@ -10753,7 +10903,7 @@
       </c>
       <c r="B237">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C237" s="98" t="s">
         <v>813</v>
@@ -10763,7 +10913,7 @@
       </c>
       <c r="E237" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999231V</v>
+        <v>110101231V</v>
       </c>
       <c r="I237" s="106"/>
     </row>
@@ -10773,7 +10923,7 @@
       </c>
       <c r="B238">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C238" s="98" t="s">
         <v>814</v>
@@ -10783,7 +10933,7 @@
       </c>
       <c r="E238" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999232X</v>
+        <v>110101232X</v>
       </c>
       <c r="I238" s="106"/>
     </row>
@@ -10793,7 +10943,7 @@
       </c>
       <c r="B239">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C239" s="98" t="s">
         <v>815</v>
@@ -10803,7 +10953,7 @@
       </c>
       <c r="E239" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999233A</v>
+        <v>110101233A</v>
       </c>
       <c r="I239" s="106"/>
     </row>
@@ -10813,7 +10963,7 @@
       </c>
       <c r="B240">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C240" s="98" t="s">
         <v>816</v>
@@ -10823,7 +10973,7 @@
       </c>
       <c r="E240" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999234H</v>
+        <v>110101234H</v>
       </c>
       <c r="I240" s="106"/>
     </row>
@@ -10833,7 +10983,7 @@
       </c>
       <c r="B241">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C241" s="98" t="s">
         <v>817</v>
@@ -10843,7 +10993,7 @@
       </c>
       <c r="E241" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999235K</v>
+        <v>110101235K</v>
       </c>
       <c r="I241" s="106"/>
     </row>
@@ -10853,7 +11003,7 @@
       </c>
       <c r="B242">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C242" s="98" t="s">
         <v>818</v>
@@ -10863,7 +11013,7 @@
       </c>
       <c r="E242" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999236M</v>
+        <v>110101236M</v>
       </c>
       <c r="I242" s="106"/>
     </row>
@@ -10873,7 +11023,7 @@
       </c>
       <c r="B243">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C243" s="98" t="s">
         <v>819</v>
@@ -10883,7 +11033,7 @@
       </c>
       <c r="E243" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999237N</v>
+        <v>110101237N</v>
       </c>
       <c r="I243" s="106"/>
     </row>
@@ -10893,7 +11043,7 @@
       </c>
       <c r="B244">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C244" s="98" t="s">
         <v>820</v>
@@ -10903,7 +11053,7 @@
       </c>
       <c r="E244" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999238R</v>
+        <v>110101238R</v>
       </c>
       <c r="I244" s="106"/>
     </row>
@@ -10913,7 +11063,7 @@
       </c>
       <c r="B245">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C245" s="98" t="s">
         <v>821</v>
@@ -10923,7 +11073,7 @@
       </c>
       <c r="E245" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999239V</v>
+        <v>110101239V</v>
       </c>
       <c r="I245" s="106"/>
     </row>
@@ -10933,7 +11083,7 @@
       </c>
       <c r="B246">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C246" s="98" t="s">
         <v>822</v>
@@ -10943,7 +11093,7 @@
       </c>
       <c r="E246" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999240X</v>
+        <v>110101240X</v>
       </c>
       <c r="I246" s="106"/>
     </row>
@@ -10953,7 +11103,7 @@
       </c>
       <c r="B247">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C247" s="98" t="s">
         <v>823</v>
@@ -10963,7 +11113,7 @@
       </c>
       <c r="E247" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999241A</v>
+        <v>110101241A</v>
       </c>
       <c r="I247" s="106"/>
     </row>
@@ -10973,7 +11123,7 @@
       </c>
       <c r="B248">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C248" s="98" t="s">
         <v>824</v>
@@ -10983,7 +11133,7 @@
       </c>
       <c r="E248" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999242H</v>
+        <v>110101242H</v>
       </c>
       <c r="I248" s="106"/>
     </row>
@@ -10993,7 +11143,7 @@
       </c>
       <c r="B249">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C249" s="98" t="s">
         <v>825</v>
@@ -11003,7 +11153,7 @@
       </c>
       <c r="E249" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999243K</v>
+        <v>110101243K</v>
       </c>
       <c r="I249" s="106"/>
     </row>
@@ -11013,7 +11163,7 @@
       </c>
       <c r="B250">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C250" s="98" t="s">
         <v>826</v>
@@ -11023,7 +11173,7 @@
       </c>
       <c r="E250" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999244M</v>
+        <v>110101244M</v>
       </c>
       <c r="I250" s="106"/>
     </row>
@@ -11033,7 +11183,7 @@
       </c>
       <c r="B251">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C251" s="98" t="s">
         <v>827</v>
@@ -11043,7 +11193,7 @@
       </c>
       <c r="E251" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999245N</v>
+        <v>110101245N</v>
       </c>
       <c r="I251" s="106"/>
     </row>
@@ -11053,7 +11203,7 @@
       </c>
       <c r="B252">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C252" s="98" t="s">
         <v>828</v>
@@ -11063,7 +11213,7 @@
       </c>
       <c r="E252" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999246R</v>
+        <v>110101246R</v>
       </c>
       <c r="I252" s="106"/>
     </row>
@@ -11073,7 +11223,7 @@
       </c>
       <c r="B253">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C253" s="98" t="s">
         <v>829</v>
@@ -11083,7 +11233,7 @@
       </c>
       <c r="E253" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999247V</v>
+        <v>110101247V</v>
       </c>
       <c r="I253" s="106"/>
     </row>
@@ -11093,7 +11243,7 @@
       </c>
       <c r="B254">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C254" s="98" t="s">
         <v>830</v>
@@ -11103,7 +11253,7 @@
       </c>
       <c r="E254" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999248X</v>
+        <v>110101248X</v>
       </c>
       <c r="I254" s="106"/>
     </row>
@@ -11113,7 +11263,7 @@
       </c>
       <c r="B255">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C255" s="98" t="s">
         <v>831</v>
@@ -11123,7 +11273,7 @@
       </c>
       <c r="E255" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999249A</v>
+        <v>110101249A</v>
       </c>
       <c r="I255" s="106"/>
     </row>
@@ -11133,7 +11283,7 @@
       </c>
       <c r="B256">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C256" s="98" t="s">
         <v>832</v>
@@ -11143,7 +11293,7 @@
       </c>
       <c r="E256" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999250H</v>
+        <v>110101250H</v>
       </c>
       <c r="I256" s="106"/>
     </row>
@@ -11153,7 +11303,7 @@
       </c>
       <c r="B257">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C257" s="98" t="s">
         <v>833</v>
@@ -11163,7 +11313,7 @@
       </c>
       <c r="E257" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999251K</v>
+        <v>110101251K</v>
       </c>
       <c r="I257" s="106"/>
     </row>
@@ -11173,7 +11323,7 @@
       </c>
       <c r="B258">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C258" s="98" t="s">
         <v>834</v>
@@ -11183,7 +11333,7 @@
       </c>
       <c r="E258" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999252M</v>
+        <v>110101252M</v>
       </c>
       <c r="I258" s="106"/>
     </row>
@@ -11193,7 +11343,7 @@
       </c>
       <c r="B259">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C259" s="98" t="s">
         <v>835</v>
@@ -11203,7 +11353,7 @@
       </c>
       <c r="E259" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999253N</v>
+        <v>110101253N</v>
       </c>
       <c r="I259" s="106"/>
     </row>
@@ -11213,7 +11363,7 @@
       </c>
       <c r="B260">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C260" s="98" t="s">
         <v>836</v>
@@ -11223,7 +11373,7 @@
       </c>
       <c r="E260" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999254R</v>
+        <v>110101254R</v>
       </c>
       <c r="I260" s="106"/>
     </row>
@@ -11233,7 +11383,7 @@
       </c>
       <c r="B261">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C261" s="98" t="s">
         <v>837</v>
@@ -11243,7 +11393,7 @@
       </c>
       <c r="E261" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999255V</v>
+        <v>110101255V</v>
       </c>
       <c r="I261" s="106"/>
     </row>
@@ -11253,7 +11403,7 @@
       </c>
       <c r="B262">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C262" s="98" t="s">
         <v>838</v>
@@ -11263,7 +11413,7 @@
       </c>
       <c r="E262" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999256X</v>
+        <v>110101256X</v>
       </c>
       <c r="I262" s="106"/>
     </row>
@@ -11273,7 +11423,7 @@
       </c>
       <c r="B263">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C263" s="98" t="s">
         <v>839</v>
@@ -11283,7 +11433,7 @@
       </c>
       <c r="E263" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999257A</v>
+        <v>110101257A</v>
       </c>
       <c r="I263" s="106"/>
     </row>
@@ -11293,7 +11443,7 @@
       </c>
       <c r="B264">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C264" s="98" t="s">
         <v>840</v>
@@ -11303,7 +11453,7 @@
       </c>
       <c r="E264" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999258H</v>
+        <v>110101258H</v>
       </c>
       <c r="I264" s="106"/>
     </row>
@@ -11313,7 +11463,7 @@
       </c>
       <c r="B265">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C265" s="98" t="s">
         <v>841</v>
@@ -11323,7 +11473,7 @@
       </c>
       <c r="E265" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999259K</v>
+        <v>110101259K</v>
       </c>
       <c r="I265" s="106"/>
     </row>
@@ -11333,7 +11483,7 @@
       </c>
       <c r="B266">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C266" s="98" t="s">
         <v>842</v>
@@ -11343,7 +11493,7 @@
       </c>
       <c r="E266" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999260M</v>
+        <v>110101260M</v>
       </c>
       <c r="I266" s="106"/>
     </row>
@@ -11353,7 +11503,7 @@
       </c>
       <c r="B267">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C267" s="98" t="s">
         <v>843</v>
@@ -11363,7 +11513,7 @@
       </c>
       <c r="E267" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999261N</v>
+        <v>110101261N</v>
       </c>
       <c r="I267" s="106"/>
     </row>
@@ -11373,7 +11523,7 @@
       </c>
       <c r="B268">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C268" s="98" t="s">
         <v>844</v>
@@ -11383,7 +11533,7 @@
       </c>
       <c r="E268" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999262R</v>
+        <v>110101262R</v>
       </c>
       <c r="I268" s="106"/>
     </row>
@@ -11393,7 +11543,7 @@
       </c>
       <c r="B269">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C269" s="98" t="s">
         <v>845</v>
@@ -11403,7 +11553,7 @@
       </c>
       <c r="E269" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999263V</v>
+        <v>110101263V</v>
       </c>
       <c r="I269" s="106"/>
     </row>
@@ -11413,7 +11563,7 @@
       </c>
       <c r="B270">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C270" s="98" t="s">
         <v>846</v>
@@ -11423,7 +11573,7 @@
       </c>
       <c r="E270" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999264X</v>
+        <v>110101264X</v>
       </c>
       <c r="I270" s="106"/>
     </row>
@@ -11433,7 +11583,7 @@
       </c>
       <c r="B271">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C271" s="98" t="s">
         <v>847</v>
@@ -11443,7 +11593,7 @@
       </c>
       <c r="E271" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999265A</v>
+        <v>110101265A</v>
       </c>
       <c r="I271" s="106"/>
     </row>
@@ -11453,7 +11603,7 @@
       </c>
       <c r="B272">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C272" s="98" t="s">
         <v>848</v>
@@ -11463,7 +11613,7 @@
       </c>
       <c r="E272" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999266H</v>
+        <v>110101266H</v>
       </c>
       <c r="I272" s="106"/>
     </row>
@@ -11473,7 +11623,7 @@
       </c>
       <c r="B273">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C273" s="98" t="s">
         <v>849</v>
@@ -11483,7 +11633,7 @@
       </c>
       <c r="E273" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999267K</v>
+        <v>110101267K</v>
       </c>
       <c r="I273" s="106"/>
     </row>
@@ -11493,7 +11643,7 @@
       </c>
       <c r="B274">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C274" s="98" t="s">
         <v>850</v>
@@ -11503,7 +11653,7 @@
       </c>
       <c r="E274" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999268M</v>
+        <v>110101268M</v>
       </c>
       <c r="I274" s="106"/>
     </row>
@@ -11513,7 +11663,7 @@
       </c>
       <c r="B275">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C275" s="98" t="s">
         <v>851</v>
@@ -11523,7 +11673,7 @@
       </c>
       <c r="E275" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999269N</v>
+        <v>110101269N</v>
       </c>
       <c r="I275" s="106"/>
     </row>
@@ -11533,7 +11683,7 @@
       </c>
       <c r="B276">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C276" s="98" t="s">
         <v>852</v>
@@ -11543,7 +11693,7 @@
       </c>
       <c r="E276" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999270R</v>
+        <v>110101270R</v>
       </c>
       <c r="I276" s="106"/>
     </row>
@@ -11553,7 +11703,7 @@
       </c>
       <c r="B277">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C277" s="98" t="s">
         <v>853</v>
@@ -11563,7 +11713,7 @@
       </c>
       <c r="E277" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999271V</v>
+        <v>110101271V</v>
       </c>
       <c r="I277" s="106"/>
     </row>
@@ -11573,7 +11723,7 @@
       </c>
       <c r="B278">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C278" s="98" t="s">
         <v>854</v>
@@ -11583,7 +11733,7 @@
       </c>
       <c r="E278" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999272X</v>
+        <v>110101272X</v>
       </c>
       <c r="I278" s="106"/>
     </row>
@@ -11593,7 +11743,7 @@
       </c>
       <c r="B279">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C279" s="98" t="s">
         <v>855</v>
@@ -11603,7 +11753,7 @@
       </c>
       <c r="E279" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999273A</v>
+        <v>110101273A</v>
       </c>
       <c r="I279" s="106"/>
     </row>
@@ -11613,7 +11763,7 @@
       </c>
       <c r="B280">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C280" s="98" t="s">
         <v>856</v>
@@ -11623,7 +11773,7 @@
       </c>
       <c r="E280" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999274H</v>
+        <v>110101274H</v>
       </c>
       <c r="I280" s="106"/>
     </row>
@@ -11633,7 +11783,7 @@
       </c>
       <c r="B281">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C281" s="98" t="s">
         <v>857</v>
@@ -11643,7 +11793,7 @@
       </c>
       <c r="E281" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999275K</v>
+        <v>110101275K</v>
       </c>
       <c r="I281" s="106"/>
     </row>
@@ -11653,7 +11803,7 @@
       </c>
       <c r="B282">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C282" s="98" t="s">
         <v>858</v>
@@ -11663,7 +11813,7 @@
       </c>
       <c r="E282" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999276M</v>
+        <v>110101276M</v>
       </c>
       <c r="I282" s="106"/>
     </row>
@@ -11673,7 +11823,7 @@
       </c>
       <c r="B283">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C283" s="98" t="s">
         <v>859</v>
@@ -11683,7 +11833,7 @@
       </c>
       <c r="E283" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999277N</v>
+        <v>110101277N</v>
       </c>
       <c r="I283" s="106"/>
     </row>
@@ -11693,7 +11843,7 @@
       </c>
       <c r="B284">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C284" s="98" t="s">
         <v>860</v>
@@ -11703,7 +11853,7 @@
       </c>
       <c r="E284" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999278R</v>
+        <v>110101278R</v>
       </c>
       <c r="I284" s="106"/>
     </row>
@@ -11713,7 +11863,7 @@
       </c>
       <c r="B285">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C285" s="98" t="s">
         <v>861</v>
@@ -11723,7 +11873,7 @@
       </c>
       <c r="E285" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999279V</v>
+        <v>110101279V</v>
       </c>
       <c r="I285" s="106"/>
     </row>
@@ -11733,7 +11883,7 @@
       </c>
       <c r="B286">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C286" s="98" t="s">
         <v>862</v>
@@ -11743,7 +11893,7 @@
       </c>
       <c r="E286" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999280X</v>
+        <v>110101280X</v>
       </c>
       <c r="I286" s="106"/>
     </row>
@@ -11753,7 +11903,7 @@
       </c>
       <c r="B287">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C287" s="98" t="s">
         <v>863</v>
@@ -11763,7 +11913,7 @@
       </c>
       <c r="E287" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999281A</v>
+        <v>110101281A</v>
       </c>
       <c r="I287" s="106"/>
     </row>
@@ -11773,7 +11923,7 @@
       </c>
       <c r="B288">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C288" s="98" t="s">
         <v>864</v>
@@ -11783,7 +11933,7 @@
       </c>
       <c r="E288" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999282H</v>
+        <v>110101282H</v>
       </c>
       <c r="I288" s="106"/>
     </row>
@@ -11793,7 +11943,7 @@
       </c>
       <c r="B289">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C289" s="98" t="s">
         <v>865</v>
@@ -11803,7 +11953,7 @@
       </c>
       <c r="E289" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999283K</v>
+        <v>110101283K</v>
       </c>
       <c r="I289" s="106"/>
     </row>
@@ -11813,7 +11963,7 @@
       </c>
       <c r="B290">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C290" s="98" t="s">
         <v>866</v>
@@ -11823,7 +11973,7 @@
       </c>
       <c r="E290" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999284M</v>
+        <v>110101284M</v>
       </c>
       <c r="I290" s="106"/>
     </row>
@@ -11833,7 +11983,7 @@
       </c>
       <c r="B291">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C291" s="98" t="s">
         <v>867</v>
@@ -11843,7 +11993,7 @@
       </c>
       <c r="E291" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999285N</v>
+        <v>110101285N</v>
       </c>
       <c r="I291" s="106"/>
     </row>
@@ -11853,7 +12003,7 @@
       </c>
       <c r="B292">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C292" s="98" t="s">
         <v>868</v>
@@ -11863,7 +12013,7 @@
       </c>
       <c r="E292" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999286R</v>
+        <v>110101286R</v>
       </c>
       <c r="I292" s="106"/>
     </row>
@@ -11873,7 +12023,7 @@
       </c>
       <c r="B293">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C293" s="98" t="s">
         <v>869</v>
@@ -11883,7 +12033,7 @@
       </c>
       <c r="E293" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999287V</v>
+        <v>110101287V</v>
       </c>
       <c r="I293" s="106"/>
     </row>
@@ -11893,7 +12043,7 @@
       </c>
       <c r="B294">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C294" s="98" t="s">
         <v>870</v>
@@ -11903,7 +12053,7 @@
       </c>
       <c r="E294" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999288X</v>
+        <v>110101288X</v>
       </c>
       <c r="I294" s="106"/>
     </row>
@@ -11913,7 +12063,7 @@
       </c>
       <c r="B295">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C295" s="98" t="s">
         <v>871</v>
@@ -11923,7 +12073,7 @@
       </c>
       <c r="E295" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999289A</v>
+        <v>110101289A</v>
       </c>
       <c r="I295" s="106"/>
     </row>
@@ -11933,7 +12083,7 @@
       </c>
       <c r="B296">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C296" s="98" t="s">
         <v>872</v>
@@ -11943,7 +12093,7 @@
       </c>
       <c r="E296" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999290H</v>
+        <v>110101290H</v>
       </c>
       <c r="I296" s="106"/>
     </row>
@@ -11953,7 +12103,7 @@
       </c>
       <c r="B297">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C297" s="98" t="s">
         <v>873</v>
@@ -11963,7 +12113,7 @@
       </c>
       <c r="E297" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999291K</v>
+        <v>110101291K</v>
       </c>
       <c r="I297" s="106"/>
     </row>
@@ -11973,7 +12123,7 @@
       </c>
       <c r="B298">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C298" s="98" t="s">
         <v>874</v>
@@ -11983,7 +12133,7 @@
       </c>
       <c r="E298" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999292M</v>
+        <v>110101292M</v>
       </c>
       <c r="I298" s="106"/>
     </row>
@@ -11993,7 +12143,7 @@
       </c>
       <c r="B299">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C299" s="98" t="s">
         <v>875</v>
@@ -12003,7 +12153,7 @@
       </c>
       <c r="E299" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999293N</v>
+        <v>110101293N</v>
       </c>
       <c r="I299" s="106"/>
     </row>
@@ -12013,7 +12163,7 @@
       </c>
       <c r="B300">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C300" s="98" t="s">
         <v>876</v>
@@ -12023,7 +12173,7 @@
       </c>
       <c r="E300" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999294R</v>
+        <v>110101294R</v>
       </c>
       <c r="I300" s="106"/>
     </row>
@@ -12033,7 +12183,7 @@
       </c>
       <c r="B301">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C301" s="98" t="s">
         <v>877</v>
@@ -12043,7 +12193,7 @@
       </c>
       <c r="E301" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999295V</v>
+        <v>110101295V</v>
       </c>
       <c r="I301" s="106"/>
     </row>
@@ -12053,7 +12203,7 @@
       </c>
       <c r="B302">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C302" s="98" t="s">
         <v>878</v>
@@ -12063,7 +12213,7 @@
       </c>
       <c r="E302" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999296X</v>
+        <v>110101296X</v>
       </c>
       <c r="I302" s="106"/>
     </row>
@@ -12073,7 +12223,7 @@
       </c>
       <c r="B303">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C303" s="98" t="s">
         <v>879</v>
@@ -12083,7 +12233,7 @@
       </c>
       <c r="E303" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999297A</v>
+        <v>110101297A</v>
       </c>
       <c r="I303" s="106"/>
     </row>
@@ -12093,7 +12243,7 @@
       </c>
       <c r="B304">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C304" s="98" t="s">
         <v>880</v>
@@ -12103,7 +12253,7 @@
       </c>
       <c r="E304" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999298H</v>
+        <v>110101298H</v>
       </c>
       <c r="I304" s="106"/>
     </row>
@@ -12113,7 +12263,7 @@
       </c>
       <c r="B305">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C305" s="98" t="s">
         <v>881</v>
@@ -12123,7 +12273,7 @@
       </c>
       <c r="E305" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999299K</v>
+        <v>110101299K</v>
       </c>
       <c r="I305" s="106"/>
     </row>
@@ -12133,7 +12283,7 @@
       </c>
       <c r="B306">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C306" s="98" t="s">
         <v>882</v>
@@ -12143,7 +12293,7 @@
       </c>
       <c r="E306" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999300M</v>
+        <v>110101300M</v>
       </c>
       <c r="I306" s="106"/>
     </row>
@@ -12153,7 +12303,7 @@
       </c>
       <c r="B307">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C307" s="98" t="s">
         <v>883</v>
@@ -12163,7 +12313,7 @@
       </c>
       <c r="E307" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999301N</v>
+        <v>110101301N</v>
       </c>
       <c r="I307" s="106"/>
     </row>
@@ -12173,7 +12323,7 @@
       </c>
       <c r="B308">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C308" s="98" t="s">
         <v>884</v>
@@ -12183,7 +12333,7 @@
       </c>
       <c r="E308" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999302R</v>
+        <v>110101302R</v>
       </c>
       <c r="I308" s="106"/>
     </row>
@@ -12193,7 +12343,7 @@
       </c>
       <c r="B309">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C309" s="98" t="s">
         <v>885</v>
@@ -12203,7 +12353,7 @@
       </c>
       <c r="E309" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999303V</v>
+        <v>110101303V</v>
       </c>
       <c r="I309" s="106"/>
     </row>
@@ -12213,7 +12363,7 @@
       </c>
       <c r="B310">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C310" s="98" t="s">
         <v>886</v>
@@ -12223,7 +12373,7 @@
       </c>
       <c r="E310" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999304X</v>
+        <v>110101304X</v>
       </c>
       <c r="I310" s="106"/>
     </row>
@@ -12233,7 +12383,7 @@
       </c>
       <c r="B311">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C311" s="98" t="s">
         <v>887</v>
@@ -12243,7 +12393,7 @@
       </c>
       <c r="E311" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999305A</v>
+        <v>110101305A</v>
       </c>
       <c r="I311" s="106"/>
     </row>
@@ -12253,7 +12403,7 @@
       </c>
       <c r="B312">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C312" s="98" t="s">
         <v>888</v>
@@ -12263,7 +12413,7 @@
       </c>
       <c r="E312" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999306H</v>
+        <v>110101306H</v>
       </c>
       <c r="I312" s="106"/>
     </row>
@@ -12273,7 +12423,7 @@
       </c>
       <c r="B313">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C313" s="98" t="s">
         <v>889</v>
@@ -12283,7 +12433,7 @@
       </c>
       <c r="E313" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999307K</v>
+        <v>110101307K</v>
       </c>
       <c r="I313" s="106"/>
     </row>
@@ -12293,7 +12443,7 @@
       </c>
       <c r="B314">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C314" s="98" t="s">
         <v>890</v>
@@ -12303,7 +12453,7 @@
       </c>
       <c r="E314" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999308M</v>
+        <v>110101308M</v>
       </c>
       <c r="I314" s="106"/>
     </row>
@@ -12313,7 +12463,7 @@
       </c>
       <c r="B315">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C315" s="98" t="s">
         <v>891</v>
@@ -12323,7 +12473,7 @@
       </c>
       <c r="E315" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999309N</v>
+        <v>110101309N</v>
       </c>
       <c r="I315" s="106"/>
     </row>
@@ -12333,7 +12483,7 @@
       </c>
       <c r="B316">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C316" s="98" t="s">
         <v>892</v>
@@ -12343,7 +12493,7 @@
       </c>
       <c r="E316" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999310R</v>
+        <v>110101310R</v>
       </c>
       <c r="I316" s="106"/>
     </row>
@@ -12353,7 +12503,7 @@
       </c>
       <c r="B317">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C317" s="98" t="s">
         <v>893</v>
@@ -12363,7 +12513,7 @@
       </c>
       <c r="E317" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999311V</v>
+        <v>110101311V</v>
       </c>
       <c r="I317" s="106"/>
     </row>
@@ -12373,7 +12523,7 @@
       </c>
       <c r="B318">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C318" s="98" t="s">
         <v>894</v>
@@ -12383,7 +12533,7 @@
       </c>
       <c r="E318" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999312X</v>
+        <v>110101312X</v>
       </c>
       <c r="I318" s="106"/>
     </row>
@@ -12393,7 +12543,7 @@
       </c>
       <c r="B319">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C319" s="98" t="s">
         <v>895</v>
@@ -12403,7 +12553,7 @@
       </c>
       <c r="E319" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999313A</v>
+        <v>110101313A</v>
       </c>
       <c r="I319" s="106"/>
     </row>
@@ -12413,7 +12563,7 @@
       </c>
       <c r="B320">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C320" s="98" t="s">
         <v>896</v>
@@ -12423,7 +12573,7 @@
       </c>
       <c r="E320" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999314H</v>
+        <v>110101314H</v>
       </c>
       <c r="I320" s="106"/>
     </row>
@@ -12433,7 +12583,7 @@
       </c>
       <c r="B321">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C321" s="98" t="s">
         <v>897</v>
@@ -12443,7 +12593,7 @@
       </c>
       <c r="E321" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999315K</v>
+        <v>110101315K</v>
       </c>
       <c r="I321" s="106"/>
     </row>
@@ -12453,7 +12603,7 @@
       </c>
       <c r="B322">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C322" s="98" t="s">
         <v>898</v>
@@ -12463,7 +12613,7 @@
       </c>
       <c r="E322" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999316M</v>
+        <v>110101316M</v>
       </c>
       <c r="I322" s="106"/>
     </row>
@@ -12473,7 +12623,7 @@
       </c>
       <c r="B323">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C323" s="98" t="s">
         <v>899</v>
@@ -12483,7 +12633,7 @@
       </c>
       <c r="E323" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999317N</v>
+        <v>110101317N</v>
       </c>
       <c r="I323" s="106"/>
     </row>
@@ -12493,7 +12643,7 @@
       </c>
       <c r="B324">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C324" s="98" t="s">
         <v>900</v>
@@ -12503,7 +12653,7 @@
       </c>
       <c r="E324" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999318R</v>
+        <v>110101318R</v>
       </c>
       <c r="I324" s="106"/>
     </row>
@@ -12513,7 +12663,7 @@
       </c>
       <c r="B325">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C325" s="98" t="s">
         <v>901</v>
@@ -12523,7 +12673,7 @@
       </c>
       <c r="E325" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999319V</v>
+        <v>110101319V</v>
       </c>
       <c r="I325" s="106"/>
     </row>
@@ -12533,7 +12683,7 @@
       </c>
       <c r="B326">
         <f ca="1">設定!$A$14</f>
-        <v>999999</v>
+        <v>110101</v>
       </c>
       <c r="C326" s="98" t="s">
         <v>902</v>
@@ -12543,7 +12693,7 @@
       </c>
       <c r="E326" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>999999320X</v>
+        <v>110101320X</v>
       </c>
       <c r="F326" s="107"/>
       <c r="G326" s="107"/>
